--- a/pantallas_android/orden_ludiyorden.xlsx
+++ b/pantallas_android/orden_ludiyorden.xlsx
@@ -1,15 +1,19 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <fileVersion appName="xl" lastEdited="5" lowestEdited="4" rupBuild="9302"/>
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="4" rupBuild="29127"/>
   <workbookPr filterPrivacy="1" defaultThemeVersion="124226"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{0F9223C5-F49D-4A5A-8E68-F72345ABFA48}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="0" yWindow="90" windowWidth="19200" windowHeight="11640" activeTab="1"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="FORMULARIO DE MTTO PREVENTIV 1" sheetId="1" r:id="rId1"/>
     <sheet name="FORMULARIO DE MTTO PREVENTIV 2" sheetId="2" r:id="rId2"/>
   </sheets>
+  <definedNames>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'FORMULARIO DE MTTO PREVENTIV 1'!$A$2:$WT$2</definedName>
+  </definedNames>
   <calcPr calcId="124519"/>
 </workbook>
 </file>
@@ -6100,7 +6104,7 @@
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
   <fonts count="2">
     <font>
       <sz val="11"/>
@@ -6174,14 +6178,17 @@
     <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{EB79DEF2-80B8-43e5-95BD-54CBDDF9020C}">
       <x14:slicerStyles defaultSlicerStyle="SlicerStyleLight1"/>
     </ext>
+    <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{9260A510-F301-46a8-8635-F512D64BE5F5}">
+      <x15:timelineStyles defaultTimelineStyle="TimeSlicerStyleLight1"/>
+    </ext>
   </extLst>
 </styleSheet>
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
-<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Tema de Office">
+<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office Theme 2007 - 2010">
   <a:themeElements>
-    <a:clrScheme name="Office">
+    <a:clrScheme name="Office 2007 - 2010">
       <a:dk1>
         <a:sysClr val="windowText" lastClr="000000"/>
       </a:dk1>
@@ -6219,7 +6226,7 @@
         <a:srgbClr val="800080"/>
       </a:folHlink>
     </a:clrScheme>
-    <a:fontScheme name="Office">
+    <a:fontScheme name="Office 2007 - 2010">
       <a:majorFont>
         <a:latin typeface="Cambria"/>
         <a:ea typeface=""/>
@@ -6291,7 +6298,7 @@
         <a:font script="Geor" typeface="Sylfaen"/>
       </a:minorFont>
     </a:fontScheme>
-    <a:fmtScheme name="Office">
+    <a:fmtScheme name="Office 2007 - 2010">
       <a:fillStyleLst>
         <a:solidFill>
           <a:schemeClr val="phClr"/>
@@ -6464,11 +6471,612 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <dimension ref="A1:WT76"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="9.140625" defaultRowHeight="15"/>
   <cols>
-    <col min="469" max="469" width="23.7109375" customWidth="1"/>
+    <col min="1" max="1" width="11.85546875" customWidth="1"/>
+    <col min="2" max="2" width="18.85546875" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="24.28515625" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="10" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="17.42578125" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="49.7109375" bestFit="1" customWidth="1"/>
+    <col min="7" max="8" width="18.42578125" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="18.7109375" bestFit="1" customWidth="1"/>
+    <col min="10" max="10" width="21.7109375" bestFit="1" customWidth="1"/>
+    <col min="11" max="11" width="23.85546875" bestFit="1" customWidth="1"/>
+    <col min="12" max="12" width="21.42578125" bestFit="1" customWidth="1"/>
+    <col min="13" max="13" width="31.5703125" bestFit="1" customWidth="1"/>
+    <col min="14" max="14" width="9" bestFit="1" customWidth="1"/>
+    <col min="15" max="15" width="39.42578125" bestFit="1" customWidth="1"/>
+    <col min="16" max="16" width="13.85546875" bestFit="1" customWidth="1"/>
+    <col min="17" max="17" width="9.28515625" bestFit="1" customWidth="1"/>
+    <col min="18" max="18" width="24.42578125" bestFit="1" customWidth="1"/>
+    <col min="19" max="20" width="47.7109375" bestFit="1" customWidth="1"/>
+    <col min="21" max="21" width="23" bestFit="1" customWidth="1"/>
+    <col min="22" max="22" width="53.5703125" bestFit="1" customWidth="1"/>
+    <col min="23" max="23" width="70.140625" bestFit="1" customWidth="1"/>
+    <col min="24" max="24" width="29.85546875" bestFit="1" customWidth="1"/>
+    <col min="25" max="25" width="47" bestFit="1" customWidth="1"/>
+    <col min="26" max="26" width="70.85546875" bestFit="1" customWidth="1"/>
+    <col min="27" max="27" width="18" bestFit="1" customWidth="1"/>
+    <col min="28" max="28" width="19.5703125" bestFit="1" customWidth="1"/>
+    <col min="29" max="29" width="18.5703125" bestFit="1" customWidth="1"/>
+    <col min="30" max="30" width="15.85546875" bestFit="1" customWidth="1"/>
+    <col min="31" max="31" width="18.42578125" bestFit="1" customWidth="1"/>
+    <col min="32" max="32" width="21.5703125" bestFit="1" customWidth="1"/>
+    <col min="33" max="33" width="17.5703125" bestFit="1" customWidth="1"/>
+    <col min="34" max="34" width="20.5703125" bestFit="1" customWidth="1"/>
+    <col min="35" max="35" width="19.140625" bestFit="1" customWidth="1"/>
+    <col min="36" max="36" width="57" bestFit="1" customWidth="1"/>
+    <col min="37" max="37" width="35" bestFit="1" customWidth="1"/>
+    <col min="38" max="38" width="21" bestFit="1" customWidth="1"/>
+    <col min="39" max="39" width="28.85546875" bestFit="1" customWidth="1"/>
+    <col min="40" max="40" width="58.28515625" bestFit="1" customWidth="1"/>
+    <col min="41" max="41" width="18.140625" bestFit="1" customWidth="1"/>
+    <col min="42" max="42" width="56" bestFit="1" customWidth="1"/>
+    <col min="43" max="43" width="36.140625" bestFit="1" customWidth="1"/>
+    <col min="44" max="44" width="29.28515625" bestFit="1" customWidth="1"/>
+    <col min="45" max="45" width="61.7109375" bestFit="1" customWidth="1"/>
+    <col min="46" max="46" width="28" bestFit="1" customWidth="1"/>
+    <col min="47" max="47" width="34.42578125" bestFit="1" customWidth="1"/>
+    <col min="48" max="48" width="37" bestFit="1" customWidth="1"/>
+    <col min="49" max="49" width="30.7109375" bestFit="1" customWidth="1"/>
+    <col min="50" max="50" width="22.5703125" bestFit="1" customWidth="1"/>
+    <col min="51" max="51" width="46" bestFit="1" customWidth="1"/>
+    <col min="52" max="52" width="54.7109375" bestFit="1" customWidth="1"/>
+    <col min="53" max="53" width="58.7109375" bestFit="1" customWidth="1"/>
+    <col min="54" max="54" width="43" bestFit="1" customWidth="1"/>
+    <col min="55" max="55" width="46" bestFit="1" customWidth="1"/>
+    <col min="56" max="56" width="54.7109375" bestFit="1" customWidth="1"/>
+    <col min="57" max="57" width="58.7109375" bestFit="1" customWidth="1"/>
+    <col min="58" max="58" width="43" bestFit="1" customWidth="1"/>
+    <col min="59" max="59" width="39.7109375" bestFit="1" customWidth="1"/>
+    <col min="60" max="60" width="55.5703125" bestFit="1" customWidth="1"/>
+    <col min="61" max="61" width="42.5703125" bestFit="1" customWidth="1"/>
+    <col min="62" max="62" width="39.5703125" bestFit="1" customWidth="1"/>
+    <col min="63" max="63" width="43.5703125" bestFit="1" customWidth="1"/>
+    <col min="64" max="64" width="30" bestFit="1" customWidth="1"/>
+    <col min="65" max="65" width="57" bestFit="1" customWidth="1"/>
+    <col min="66" max="66" width="21" bestFit="1" customWidth="1"/>
+    <col min="67" max="67" width="23.85546875" bestFit="1" customWidth="1"/>
+    <col min="68" max="68" width="50.42578125" bestFit="1" customWidth="1"/>
+    <col min="69" max="69" width="39.140625" bestFit="1" customWidth="1"/>
+    <col min="70" max="70" width="57.85546875" bestFit="1" customWidth="1"/>
+    <col min="71" max="71" width="45" bestFit="1" customWidth="1"/>
+    <col min="72" max="72" width="57.5703125" bestFit="1" customWidth="1"/>
+    <col min="73" max="73" width="61.7109375" bestFit="1" customWidth="1"/>
+    <col min="74" max="74" width="45.140625" bestFit="1" customWidth="1"/>
+    <col min="75" max="75" width="34.5703125" bestFit="1" customWidth="1"/>
+    <col min="76" max="76" width="42.140625" bestFit="1" customWidth="1"/>
+    <col min="77" max="77" width="47.7109375" bestFit="1" customWidth="1"/>
+    <col min="78" max="78" width="36.28515625" bestFit="1" customWidth="1"/>
+    <col min="79" max="79" width="42.85546875" bestFit="1" customWidth="1"/>
+    <col min="80" max="80" width="55.140625" bestFit="1" customWidth="1"/>
+    <col min="81" max="81" width="54.7109375" bestFit="1" customWidth="1"/>
+    <col min="82" max="82" width="54.5703125" bestFit="1" customWidth="1"/>
+    <col min="83" max="83" width="53.85546875" bestFit="1" customWidth="1"/>
+    <col min="84" max="84" width="44.140625" bestFit="1" customWidth="1"/>
+    <col min="85" max="85" width="52.28515625" bestFit="1" customWidth="1"/>
+    <col min="86" max="86" width="50.5703125" bestFit="1" customWidth="1"/>
+    <col min="87" max="87" width="40.140625" bestFit="1" customWidth="1"/>
+    <col min="88" max="88" width="35.42578125" bestFit="1" customWidth="1"/>
+    <col min="89" max="89" width="52.5703125" bestFit="1" customWidth="1"/>
+    <col min="90" max="90" width="51.7109375" bestFit="1" customWidth="1"/>
+    <col min="91" max="91" width="31.5703125" bestFit="1" customWidth="1"/>
+    <col min="92" max="92" width="33" bestFit="1" customWidth="1"/>
+    <col min="93" max="93" width="39.85546875" bestFit="1" customWidth="1"/>
+    <col min="94" max="94" width="53.28515625" bestFit="1" customWidth="1"/>
+    <col min="95" max="95" width="50.5703125" bestFit="1" customWidth="1"/>
+    <col min="96" max="96" width="60.85546875" bestFit="1" customWidth="1"/>
+    <col min="97" max="97" width="43" bestFit="1" customWidth="1"/>
+    <col min="98" max="98" width="53.5703125" bestFit="1" customWidth="1"/>
+    <col min="99" max="99" width="60.85546875" bestFit="1" customWidth="1"/>
+    <col min="100" max="100" width="26.85546875" bestFit="1" customWidth="1"/>
+    <col min="101" max="101" width="19.42578125" bestFit="1" customWidth="1"/>
+    <col min="102" max="102" width="56.42578125" bestFit="1" customWidth="1"/>
+    <col min="103" max="103" width="55.85546875" bestFit="1" customWidth="1"/>
+    <col min="104" max="104" width="28.85546875" bestFit="1" customWidth="1"/>
+    <col min="105" max="105" width="43.42578125" bestFit="1" customWidth="1"/>
+    <col min="106" max="106" width="31.5703125" bestFit="1" customWidth="1"/>
+    <col min="107" max="107" width="39" bestFit="1" customWidth="1"/>
+    <col min="108" max="108" width="32.140625" bestFit="1" customWidth="1"/>
+    <col min="109" max="109" width="54.28515625" bestFit="1" customWidth="1"/>
+    <col min="110" max="110" width="52.5703125" bestFit="1" customWidth="1"/>
+    <col min="111" max="111" width="37.7109375" bestFit="1" customWidth="1"/>
+    <col min="112" max="112" width="30.42578125" bestFit="1" customWidth="1"/>
+    <col min="113" max="113" width="30.7109375" bestFit="1" customWidth="1"/>
+    <col min="114" max="114" width="56.42578125" bestFit="1" customWidth="1"/>
+    <col min="115" max="115" width="59.28515625" bestFit="1" customWidth="1"/>
+    <col min="116" max="116" width="23.140625" bestFit="1" customWidth="1"/>
+    <col min="117" max="117" width="56.7109375" bestFit="1" customWidth="1"/>
+    <col min="118" max="118" width="42.85546875" bestFit="1" customWidth="1"/>
+    <col min="119" max="119" width="21" bestFit="1" customWidth="1"/>
+    <col min="120" max="120" width="50.7109375" bestFit="1" customWidth="1"/>
+    <col min="121" max="121" width="58.42578125" bestFit="1" customWidth="1"/>
+    <col min="122" max="122" width="32.5703125" bestFit="1" customWidth="1"/>
+    <col min="123" max="123" width="38.28515625" bestFit="1" customWidth="1"/>
+    <col min="124" max="124" width="47.28515625" bestFit="1" customWidth="1"/>
+    <col min="125" max="125" width="43.7109375" bestFit="1" customWidth="1"/>
+    <col min="126" max="126" width="44" bestFit="1" customWidth="1"/>
+    <col min="127" max="127" width="29" bestFit="1" customWidth="1"/>
+    <col min="128" max="128" width="29.28515625" bestFit="1" customWidth="1"/>
+    <col min="129" max="129" width="33.28515625" bestFit="1" customWidth="1"/>
+    <col min="130" max="130" width="18.85546875" bestFit="1" customWidth="1"/>
+    <col min="131" max="131" width="51.28515625" bestFit="1" customWidth="1"/>
+    <col min="132" max="132" width="56.42578125" bestFit="1" customWidth="1"/>
+    <col min="133" max="133" width="55" bestFit="1" customWidth="1"/>
+    <col min="134" max="134" width="53.85546875" bestFit="1" customWidth="1"/>
+    <col min="135" max="135" width="29.7109375" bestFit="1" customWidth="1"/>
+    <col min="136" max="136" width="19.85546875" bestFit="1" customWidth="1"/>
+    <col min="137" max="137" width="41" bestFit="1" customWidth="1"/>
+    <col min="138" max="138" width="30.28515625" bestFit="1" customWidth="1"/>
+    <col min="139" max="139" width="39.85546875" bestFit="1" customWidth="1"/>
+    <col min="140" max="140" width="58.85546875" bestFit="1" customWidth="1"/>
+    <col min="141" max="141" width="39" bestFit="1" customWidth="1"/>
+    <col min="142" max="142" width="27.42578125" bestFit="1" customWidth="1"/>
+    <col min="143" max="143" width="37.42578125" bestFit="1" customWidth="1"/>
+    <col min="144" max="144" width="53.140625" bestFit="1" customWidth="1"/>
+    <col min="145" max="145" width="37.42578125" bestFit="1" customWidth="1"/>
+    <col min="146" max="146" width="28.85546875" bestFit="1" customWidth="1"/>
+    <col min="147" max="147" width="47" bestFit="1" customWidth="1"/>
+    <col min="148" max="148" width="39.5703125" bestFit="1" customWidth="1"/>
+    <col min="149" max="149" width="40.42578125" bestFit="1" customWidth="1"/>
+    <col min="150" max="150" width="44.5703125" bestFit="1" customWidth="1"/>
+    <col min="151" max="151" width="32.28515625" bestFit="1" customWidth="1"/>
+    <col min="152" max="152" width="49" bestFit="1" customWidth="1"/>
+    <col min="153" max="153" width="44.42578125" bestFit="1" customWidth="1"/>
+    <col min="154" max="154" width="48.7109375" bestFit="1" customWidth="1"/>
+    <col min="155" max="155" width="54.85546875" bestFit="1" customWidth="1"/>
+    <col min="156" max="156" width="51.7109375" bestFit="1" customWidth="1"/>
+    <col min="157" max="157" width="48.7109375" bestFit="1" customWidth="1"/>
+    <col min="158" max="158" width="46.140625" bestFit="1" customWidth="1"/>
+    <col min="159" max="159" width="33.5703125" bestFit="1" customWidth="1"/>
+    <col min="160" max="160" width="32.28515625" bestFit="1" customWidth="1"/>
+    <col min="161" max="161" width="53.7109375" bestFit="1" customWidth="1"/>
+    <col min="162" max="162" width="48.7109375" bestFit="1" customWidth="1"/>
+    <col min="163" max="163" width="56.28515625" bestFit="1" customWidth="1"/>
+    <col min="164" max="164" width="51.28515625" bestFit="1" customWidth="1"/>
+    <col min="165" max="165" width="61.28515625" bestFit="1" customWidth="1"/>
+    <col min="166" max="166" width="59.5703125" bestFit="1" customWidth="1"/>
+    <col min="167" max="167" width="56.85546875" bestFit="1" customWidth="1"/>
+    <col min="168" max="169" width="57.42578125" bestFit="1" customWidth="1"/>
+    <col min="170" max="170" width="34.85546875" bestFit="1" customWidth="1"/>
+    <col min="171" max="171" width="32.140625" bestFit="1" customWidth="1"/>
+    <col min="172" max="172" width="40.42578125" bestFit="1" customWidth="1"/>
+    <col min="173" max="173" width="21.85546875" bestFit="1" customWidth="1"/>
+    <col min="174" max="174" width="20.5703125" bestFit="1" customWidth="1"/>
+    <col min="175" max="175" width="66.85546875" bestFit="1" customWidth="1"/>
+    <col min="176" max="176" width="58.140625" bestFit="1" customWidth="1"/>
+    <col min="177" max="177" width="56" bestFit="1" customWidth="1"/>
+    <col min="178" max="178" width="42.42578125" bestFit="1" customWidth="1"/>
+    <col min="179" max="179" width="49.28515625" bestFit="1" customWidth="1"/>
+    <col min="180" max="180" width="55.5703125" bestFit="1" customWidth="1"/>
+    <col min="181" max="181" width="29.5703125" bestFit="1" customWidth="1"/>
+    <col min="182" max="182" width="41.85546875" bestFit="1" customWidth="1"/>
+    <col min="183" max="183" width="50.5703125" bestFit="1" customWidth="1"/>
+    <col min="184" max="184" width="42.7109375" bestFit="1" customWidth="1"/>
+    <col min="185" max="185" width="56.140625" bestFit="1" customWidth="1"/>
+    <col min="186" max="186" width="25" bestFit="1" customWidth="1"/>
+    <col min="187" max="187" width="60" bestFit="1" customWidth="1"/>
+    <col min="188" max="188" width="50.7109375" bestFit="1" customWidth="1"/>
+    <col min="189" max="189" width="80.28515625" bestFit="1" customWidth="1"/>
+    <col min="190" max="190" width="41.28515625" bestFit="1" customWidth="1"/>
+    <col min="191" max="191" width="52.28515625" bestFit="1" customWidth="1"/>
+    <col min="192" max="192" width="36.28515625" bestFit="1" customWidth="1"/>
+    <col min="193" max="193" width="58.42578125" bestFit="1" customWidth="1"/>
+    <col min="194" max="194" width="50.42578125" bestFit="1" customWidth="1"/>
+    <col min="195" max="195" width="49.5703125" bestFit="1" customWidth="1"/>
+    <col min="196" max="196" width="60.85546875" bestFit="1" customWidth="1"/>
+    <col min="197" max="197" width="54.5703125" bestFit="1" customWidth="1"/>
+    <col min="198" max="198" width="55.85546875" bestFit="1" customWidth="1"/>
+    <col min="199" max="199" width="58.85546875" bestFit="1" customWidth="1"/>
+    <col min="200" max="200" width="43.85546875" bestFit="1" customWidth="1"/>
+    <col min="201" max="201" width="49.5703125" bestFit="1" customWidth="1"/>
+    <col min="202" max="202" width="30.42578125" bestFit="1" customWidth="1"/>
+    <col min="203" max="203" width="32.7109375" bestFit="1" customWidth="1"/>
+    <col min="204" max="204" width="46.5703125" bestFit="1" customWidth="1"/>
+    <col min="205" max="205" width="50.7109375" bestFit="1" customWidth="1"/>
+    <col min="206" max="206" width="37.5703125" bestFit="1" customWidth="1"/>
+    <col min="207" max="207" width="51.140625" bestFit="1" customWidth="1"/>
+    <col min="208" max="208" width="40.28515625" bestFit="1" customWidth="1"/>
+    <col min="209" max="209" width="55" bestFit="1" customWidth="1"/>
+    <col min="210" max="210" width="54.140625" bestFit="1" customWidth="1"/>
+    <col min="211" max="211" width="35.28515625" bestFit="1" customWidth="1"/>
+    <col min="212" max="212" width="41.140625" bestFit="1" customWidth="1"/>
+    <col min="213" max="213" width="54.140625" bestFit="1" customWidth="1"/>
+    <col min="214" max="214" width="57" bestFit="1" customWidth="1"/>
+    <col min="215" max="215" width="56.140625" bestFit="1" customWidth="1"/>
+    <col min="216" max="216" width="47" bestFit="1" customWidth="1"/>
+    <col min="217" max="217" width="37.5703125" bestFit="1" customWidth="1"/>
+    <col min="218" max="218" width="30.140625" bestFit="1" customWidth="1"/>
+    <col min="219" max="219" width="49.7109375" bestFit="1" customWidth="1"/>
+    <col min="220" max="220" width="46.28515625" bestFit="1" customWidth="1"/>
+    <col min="221" max="221" width="56.140625" bestFit="1" customWidth="1"/>
+    <col min="222" max="222" width="39.28515625" bestFit="1" customWidth="1"/>
+    <col min="223" max="223" width="44.85546875" bestFit="1" customWidth="1"/>
+    <col min="224" max="224" width="49.140625" bestFit="1" customWidth="1"/>
+    <col min="225" max="225" width="45.42578125" bestFit="1" customWidth="1"/>
+    <col min="226" max="226" width="44.85546875" bestFit="1" customWidth="1"/>
+    <col min="227" max="227" width="55" bestFit="1" customWidth="1"/>
+    <col min="228" max="228" width="43.5703125" bestFit="1" customWidth="1"/>
+    <col min="229" max="229" width="38.85546875" bestFit="1" customWidth="1"/>
+    <col min="230" max="230" width="56.5703125" bestFit="1" customWidth="1"/>
+    <col min="231" max="231" width="33.5703125" bestFit="1" customWidth="1"/>
+    <col min="232" max="232" width="47.28515625" bestFit="1" customWidth="1"/>
+    <col min="233" max="233" width="59.28515625" bestFit="1" customWidth="1"/>
+    <col min="234" max="234" width="13.85546875" bestFit="1" customWidth="1"/>
+    <col min="235" max="235" width="30.7109375" bestFit="1" customWidth="1"/>
+    <col min="236" max="236" width="26" bestFit="1" customWidth="1"/>
+    <col min="237" max="237" width="25.140625" bestFit="1" customWidth="1"/>
+    <col min="238" max="238" width="67" bestFit="1" customWidth="1"/>
+    <col min="239" max="239" width="52.42578125" bestFit="1" customWidth="1"/>
+    <col min="240" max="240" width="50.5703125" bestFit="1" customWidth="1"/>
+    <col min="241" max="241" width="51" bestFit="1" customWidth="1"/>
+    <col min="242" max="242" width="47.85546875" bestFit="1" customWidth="1"/>
+    <col min="243" max="243" width="42.7109375" bestFit="1" customWidth="1"/>
+    <col min="244" max="244" width="55" bestFit="1" customWidth="1"/>
+    <col min="245" max="245" width="50" bestFit="1" customWidth="1"/>
+    <col min="246" max="246" width="46.140625" bestFit="1" customWidth="1"/>
+    <col min="247" max="247" width="52.5703125" bestFit="1" customWidth="1"/>
+    <col min="248" max="248" width="44.140625" bestFit="1" customWidth="1"/>
+    <col min="249" max="249" width="33" bestFit="1" customWidth="1"/>
+    <col min="250" max="250" width="38.5703125" bestFit="1" customWidth="1"/>
+    <col min="251" max="251" width="48.85546875" bestFit="1" customWidth="1"/>
+    <col min="252" max="252" width="47.5703125" bestFit="1" customWidth="1"/>
+    <col min="253" max="253" width="13.140625" bestFit="1" customWidth="1"/>
+    <col min="254" max="254" width="31" bestFit="1" customWidth="1"/>
+    <col min="255" max="255" width="38.7109375" bestFit="1" customWidth="1"/>
+    <col min="256" max="256" width="31.85546875" bestFit="1" customWidth="1"/>
+    <col min="257" max="257" width="31.28515625" bestFit="1" customWidth="1"/>
+    <col min="258" max="258" width="58.42578125" bestFit="1" customWidth="1"/>
+    <col min="259" max="259" width="40" bestFit="1" customWidth="1"/>
+    <col min="260" max="260" width="24.28515625" bestFit="1" customWidth="1"/>
+    <col min="261" max="261" width="24.140625" bestFit="1" customWidth="1"/>
+    <col min="262" max="262" width="27.5703125" bestFit="1" customWidth="1"/>
+    <col min="263" max="263" width="36.140625" bestFit="1" customWidth="1"/>
+    <col min="264" max="264" width="36" bestFit="1" customWidth="1"/>
+    <col min="265" max="265" width="21.42578125" bestFit="1" customWidth="1"/>
+    <col min="266" max="266" width="18.42578125" bestFit="1" customWidth="1"/>
+    <col min="267" max="267" width="29.5703125" bestFit="1" customWidth="1"/>
+    <col min="268" max="268" width="61.85546875" bestFit="1" customWidth="1"/>
+    <col min="269" max="269" width="22.140625" bestFit="1" customWidth="1"/>
+    <col min="270" max="270" width="57" bestFit="1" customWidth="1"/>
+    <col min="271" max="271" width="56.140625" bestFit="1" customWidth="1"/>
+    <col min="272" max="272" width="29.140625" bestFit="1" customWidth="1"/>
+    <col min="273" max="273" width="21.42578125" bestFit="1" customWidth="1"/>
+    <col min="274" max="274" width="38.140625" bestFit="1" customWidth="1"/>
+    <col min="275" max="275" width="19.140625" bestFit="1" customWidth="1"/>
+    <col min="276" max="276" width="27.85546875" bestFit="1" customWidth="1"/>
+    <col min="277" max="277" width="57.7109375" bestFit="1" customWidth="1"/>
+    <col min="278" max="278" width="25.28515625" bestFit="1" customWidth="1"/>
+    <col min="279" max="279" width="36.7109375" bestFit="1" customWidth="1"/>
+    <col min="280" max="280" width="52.7109375" bestFit="1" customWidth="1"/>
+    <col min="281" max="281" width="13.42578125" bestFit="1" customWidth="1"/>
+    <col min="282" max="282" width="56.7109375" bestFit="1" customWidth="1"/>
+    <col min="283" max="283" width="52.7109375" bestFit="1" customWidth="1"/>
+    <col min="284" max="284" width="22.7109375" bestFit="1" customWidth="1"/>
+    <col min="285" max="285" width="40.42578125" bestFit="1" customWidth="1"/>
+    <col min="286" max="286" width="39.5703125" bestFit="1" customWidth="1"/>
+    <col min="287" max="287" width="25" bestFit="1" customWidth="1"/>
+    <col min="288" max="288" width="53.28515625" bestFit="1" customWidth="1"/>
+    <col min="289" max="289" width="66.85546875" bestFit="1" customWidth="1"/>
+    <col min="290" max="290" width="30.5703125" bestFit="1" customWidth="1"/>
+    <col min="291" max="291" width="29.85546875" bestFit="1" customWidth="1"/>
+    <col min="292" max="292" width="19.5703125" bestFit="1" customWidth="1"/>
+    <col min="293" max="293" width="38" bestFit="1" customWidth="1"/>
+    <col min="294" max="294" width="24.5703125" bestFit="1" customWidth="1"/>
+    <col min="295" max="295" width="19.28515625" bestFit="1" customWidth="1"/>
+    <col min="296" max="296" width="23.85546875" bestFit="1" customWidth="1"/>
+    <col min="297" max="297" width="30.7109375" bestFit="1" customWidth="1"/>
+    <col min="298" max="298" width="28.28515625" bestFit="1" customWidth="1"/>
+    <col min="299" max="299" width="54.42578125" bestFit="1" customWidth="1"/>
+    <col min="300" max="300" width="40" bestFit="1" customWidth="1"/>
+    <col min="301" max="301" width="40.42578125" bestFit="1" customWidth="1"/>
+    <col min="302" max="302" width="37" bestFit="1" customWidth="1"/>
+    <col min="303" max="303" width="11.85546875" bestFit="1" customWidth="1"/>
+    <col min="304" max="304" width="45" bestFit="1" customWidth="1"/>
+    <col min="305" max="305" width="43.7109375" bestFit="1" customWidth="1"/>
+    <col min="306" max="306" width="21" bestFit="1" customWidth="1"/>
+    <col min="307" max="307" width="54.85546875" bestFit="1" customWidth="1"/>
+    <col min="308" max="308" width="43.28515625" bestFit="1" customWidth="1"/>
+    <col min="309" max="309" width="29" bestFit="1" customWidth="1"/>
+    <col min="310" max="310" width="40.85546875" bestFit="1" customWidth="1"/>
+    <col min="311" max="311" width="50.140625" bestFit="1" customWidth="1"/>
+    <col min="312" max="312" width="53.140625" bestFit="1" customWidth="1"/>
+    <col min="313" max="313" width="42.5703125" bestFit="1" customWidth="1"/>
+    <col min="314" max="314" width="39.85546875" bestFit="1" customWidth="1"/>
+    <col min="315" max="315" width="34.42578125" bestFit="1" customWidth="1"/>
+    <col min="316" max="316" width="44.5703125" bestFit="1" customWidth="1"/>
+    <col min="317" max="317" width="47.140625" bestFit="1" customWidth="1"/>
+    <col min="318" max="318" width="18.28515625" bestFit="1" customWidth="1"/>
+    <col min="319" max="319" width="25" bestFit="1" customWidth="1"/>
+    <col min="320" max="320" width="56.42578125" bestFit="1" customWidth="1"/>
+    <col min="321" max="321" width="28.85546875" bestFit="1" customWidth="1"/>
+    <col min="322" max="322" width="21" bestFit="1" customWidth="1"/>
+    <col min="323" max="323" width="38.28515625" bestFit="1" customWidth="1"/>
+    <col min="324" max="324" width="24.42578125" bestFit="1" customWidth="1"/>
+    <col min="325" max="325" width="18.85546875" bestFit="1" customWidth="1"/>
+    <col min="326" max="326" width="30.28515625" bestFit="1" customWidth="1"/>
+    <col min="327" max="327" width="32.7109375" bestFit="1" customWidth="1"/>
+    <col min="328" max="328" width="29.7109375" bestFit="1" customWidth="1"/>
+    <col min="329" max="329" width="56" bestFit="1" customWidth="1"/>
+    <col min="330" max="330" width="49.5703125" bestFit="1" customWidth="1"/>
+    <col min="331" max="331" width="44.5703125" bestFit="1" customWidth="1"/>
+    <col min="332" max="332" width="24.140625" bestFit="1" customWidth="1"/>
+    <col min="333" max="333" width="30.5703125" bestFit="1" customWidth="1"/>
+    <col min="334" max="334" width="30.7109375" bestFit="1" customWidth="1"/>
+    <col min="335" max="335" width="45" bestFit="1" customWidth="1"/>
+    <col min="336" max="336" width="49.5703125" bestFit="1" customWidth="1"/>
+    <col min="337" max="337" width="49.28515625" bestFit="1" customWidth="1"/>
+    <col min="338" max="338" width="44.85546875" bestFit="1" customWidth="1"/>
+    <col min="339" max="339" width="51" bestFit="1" customWidth="1"/>
+    <col min="340" max="340" width="52.5703125" bestFit="1" customWidth="1"/>
+    <col min="341" max="341" width="39.28515625" bestFit="1" customWidth="1"/>
+    <col min="342" max="342" width="44.42578125" bestFit="1" customWidth="1"/>
+    <col min="343" max="343" width="22.28515625" bestFit="1" customWidth="1"/>
+    <col min="344" max="344" width="55.28515625" bestFit="1" customWidth="1"/>
+    <col min="345" max="345" width="55.85546875" bestFit="1" customWidth="1"/>
+    <col min="346" max="346" width="44" bestFit="1" customWidth="1"/>
+    <col min="347" max="350" width="33.7109375" bestFit="1" customWidth="1"/>
+    <col min="351" max="351" width="51.7109375" bestFit="1" customWidth="1"/>
+    <col min="352" max="352" width="24.85546875" bestFit="1" customWidth="1"/>
+    <col min="353" max="353" width="27.7109375" bestFit="1" customWidth="1"/>
+    <col min="354" max="354" width="56.5703125" bestFit="1" customWidth="1"/>
+    <col min="355" max="355" width="55.140625" bestFit="1" customWidth="1"/>
+    <col min="356" max="356" width="57.28515625" bestFit="1" customWidth="1"/>
+    <col min="357" max="357" width="56.5703125" bestFit="1" customWidth="1"/>
+    <col min="358" max="358" width="56" bestFit="1" customWidth="1"/>
+    <col min="359" max="359" width="46.140625" bestFit="1" customWidth="1"/>
+    <col min="360" max="360" width="47.28515625" bestFit="1" customWidth="1"/>
+    <col min="361" max="361" width="33.85546875" bestFit="1" customWidth="1"/>
+    <col min="362" max="362" width="21.85546875" bestFit="1" customWidth="1"/>
+    <col min="363" max="363" width="49.42578125" bestFit="1" customWidth="1"/>
+    <col min="364" max="364" width="56.140625" bestFit="1" customWidth="1"/>
+    <col min="365" max="365" width="33.140625" bestFit="1" customWidth="1"/>
+    <col min="366" max="366" width="25.140625" bestFit="1" customWidth="1"/>
+    <col min="367" max="367" width="29" bestFit="1" customWidth="1"/>
+    <col min="368" max="368" width="29.7109375" bestFit="1" customWidth="1"/>
+    <col min="369" max="369" width="33.42578125" bestFit="1" customWidth="1"/>
+    <col min="370" max="370" width="32.28515625" bestFit="1" customWidth="1"/>
+    <col min="371" max="371" width="35.5703125" bestFit="1" customWidth="1"/>
+    <col min="372" max="372" width="42.7109375" bestFit="1" customWidth="1"/>
+    <col min="373" max="373" width="63" bestFit="1" customWidth="1"/>
+    <col min="374" max="374" width="21.7109375" bestFit="1" customWidth="1"/>
+    <col min="375" max="375" width="56.7109375" bestFit="1" customWidth="1"/>
+    <col min="376" max="376" width="40.5703125" bestFit="1" customWidth="1"/>
+    <col min="377" max="377" width="56" bestFit="1" customWidth="1"/>
+    <col min="378" max="378" width="40.5703125" bestFit="1" customWidth="1"/>
+    <col min="379" max="379" width="61.140625" bestFit="1" customWidth="1"/>
+    <col min="380" max="380" width="30.85546875" bestFit="1" customWidth="1"/>
+    <col min="381" max="381" width="56.7109375" bestFit="1" customWidth="1"/>
+    <col min="382" max="382" width="100" bestFit="1" customWidth="1"/>
+    <col min="383" max="383" width="32.42578125" bestFit="1" customWidth="1"/>
+    <col min="384" max="384" width="54" bestFit="1" customWidth="1"/>
+    <col min="385" max="385" width="43.7109375" bestFit="1" customWidth="1"/>
+    <col min="386" max="386" width="36" bestFit="1" customWidth="1"/>
+    <col min="387" max="387" width="60.140625" bestFit="1" customWidth="1"/>
+    <col min="388" max="388" width="35.5703125" bestFit="1" customWidth="1"/>
+    <col min="389" max="389" width="50.28515625" bestFit="1" customWidth="1"/>
+    <col min="390" max="390" width="39.28515625" bestFit="1" customWidth="1"/>
+    <col min="391" max="391" width="20.7109375" bestFit="1" customWidth="1"/>
+    <col min="392" max="392" width="20.28515625" bestFit="1" customWidth="1"/>
+    <col min="393" max="393" width="54.28515625" bestFit="1" customWidth="1"/>
+    <col min="394" max="394" width="30.85546875" bestFit="1" customWidth="1"/>
+    <col min="395" max="395" width="36.85546875" bestFit="1" customWidth="1"/>
+    <col min="396" max="396" width="29.42578125" bestFit="1" customWidth="1"/>
+    <col min="397" max="397" width="62.140625" bestFit="1" customWidth="1"/>
+    <col min="398" max="398" width="34.7109375" bestFit="1" customWidth="1"/>
+    <col min="399" max="399" width="35" bestFit="1" customWidth="1"/>
+    <col min="400" max="400" width="59.28515625" bestFit="1" customWidth="1"/>
+    <col min="401" max="401" width="49.140625" bestFit="1" customWidth="1"/>
+    <col min="402" max="402" width="27.140625" bestFit="1" customWidth="1"/>
+    <col min="403" max="403" width="56.85546875" bestFit="1" customWidth="1"/>
+    <col min="404" max="404" width="43.42578125" bestFit="1" customWidth="1"/>
+    <col min="405" max="405" width="37.85546875" bestFit="1" customWidth="1"/>
+    <col min="406" max="406" width="27.28515625" bestFit="1" customWidth="1"/>
+    <col min="407" max="407" width="40.85546875" bestFit="1" customWidth="1"/>
+    <col min="408" max="408" width="49.28515625" bestFit="1" customWidth="1"/>
+    <col min="409" max="410" width="49" bestFit="1" customWidth="1"/>
+    <col min="411" max="411" width="40.5703125" bestFit="1" customWidth="1"/>
+    <col min="412" max="412" width="39.28515625" bestFit="1" customWidth="1"/>
+    <col min="413" max="413" width="51.5703125" bestFit="1" customWidth="1"/>
+    <col min="414" max="414" width="41.5703125" bestFit="1" customWidth="1"/>
+    <col min="415" max="415" width="38.42578125" bestFit="1" customWidth="1"/>
+    <col min="416" max="416" width="44.5703125" bestFit="1" customWidth="1"/>
+    <col min="417" max="417" width="34.85546875" bestFit="1" customWidth="1"/>
+    <col min="418" max="418" width="46.28515625" bestFit="1" customWidth="1"/>
+    <col min="419" max="419" width="40.85546875" bestFit="1" customWidth="1"/>
+    <col min="420" max="420" width="56.28515625" bestFit="1" customWidth="1"/>
+    <col min="421" max="421" width="49.85546875" bestFit="1" customWidth="1"/>
+    <col min="422" max="422" width="63.42578125" bestFit="1" customWidth="1"/>
+    <col min="423" max="423" width="55.85546875" bestFit="1" customWidth="1"/>
+    <col min="424" max="424" width="54.28515625" bestFit="1" customWidth="1"/>
+    <col min="425" max="425" width="38.85546875" bestFit="1" customWidth="1"/>
+    <col min="426" max="426" width="51.140625" bestFit="1" customWidth="1"/>
+    <col min="427" max="427" width="53.28515625" bestFit="1" customWidth="1"/>
+    <col min="428" max="428" width="40.28515625" bestFit="1" customWidth="1"/>
+    <col min="429" max="429" width="36.28515625" bestFit="1" customWidth="1"/>
+    <col min="430" max="430" width="43.28515625" bestFit="1" customWidth="1"/>
+    <col min="431" max="431" width="58.42578125" bestFit="1" customWidth="1"/>
+    <col min="432" max="432" width="43.7109375" bestFit="1" customWidth="1"/>
+    <col min="433" max="433" width="31.140625" bestFit="1" customWidth="1"/>
+    <col min="434" max="434" width="59.7109375" bestFit="1" customWidth="1"/>
+    <col min="435" max="435" width="58.140625" bestFit="1" customWidth="1"/>
+    <col min="436" max="436" width="59.7109375" bestFit="1" customWidth="1"/>
+    <col min="437" max="437" width="29.28515625" bestFit="1" customWidth="1"/>
+    <col min="438" max="438" width="29.85546875" bestFit="1" customWidth="1"/>
+    <col min="439" max="439" width="43.7109375" bestFit="1" customWidth="1"/>
+    <col min="440" max="440" width="21.5703125" bestFit="1" customWidth="1"/>
+    <col min="441" max="441" width="26.7109375" bestFit="1" customWidth="1"/>
+    <col min="442" max="442" width="37.7109375" bestFit="1" customWidth="1"/>
+    <col min="443" max="443" width="22.42578125" bestFit="1" customWidth="1"/>
+    <col min="444" max="444" width="18.7109375" bestFit="1" customWidth="1"/>
+    <col min="445" max="445" width="37.7109375" bestFit="1" customWidth="1"/>
+    <col min="446" max="446" width="32.5703125" bestFit="1" customWidth="1"/>
+    <col min="447" max="447" width="29.140625" bestFit="1" customWidth="1"/>
+    <col min="448" max="448" width="56" bestFit="1" customWidth="1"/>
+    <col min="449" max="449" width="21.7109375" bestFit="1" customWidth="1"/>
+    <col min="450" max="450" width="22.7109375" bestFit="1" customWidth="1"/>
+    <col min="451" max="451" width="33" bestFit="1" customWidth="1"/>
+    <col min="452" max="452" width="36" bestFit="1" customWidth="1"/>
+    <col min="453" max="453" width="19.7109375" bestFit="1" customWidth="1"/>
+    <col min="454" max="454" width="24.5703125" bestFit="1" customWidth="1"/>
+    <col min="455" max="455" width="24.7109375" bestFit="1" customWidth="1"/>
+    <col min="456" max="456" width="48.42578125" bestFit="1" customWidth="1"/>
+    <col min="457" max="457" width="31" bestFit="1" customWidth="1"/>
+    <col min="458" max="459" width="37.5703125" bestFit="1" customWidth="1"/>
+    <col min="460" max="460" width="25.140625" bestFit="1" customWidth="1"/>
+    <col min="461" max="462" width="33.28515625" bestFit="1" customWidth="1"/>
+    <col min="463" max="463" width="28.85546875" bestFit="1" customWidth="1"/>
+    <col min="464" max="466" width="26" bestFit="1" customWidth="1"/>
+    <col min="467" max="468" width="33.140625" bestFit="1" customWidth="1"/>
+    <col min="469" max="469" width="38.5703125" bestFit="1" customWidth="1"/>
+    <col min="470" max="472" width="38.28515625" bestFit="1" customWidth="1"/>
+    <col min="473" max="473" width="37.140625" bestFit="1" customWidth="1"/>
+    <col min="474" max="474" width="35.7109375" bestFit="1" customWidth="1"/>
+    <col min="475" max="475" width="46.140625" bestFit="1" customWidth="1"/>
+    <col min="476" max="476" width="24.5703125" bestFit="1" customWidth="1"/>
+    <col min="477" max="477" width="26.7109375" bestFit="1" customWidth="1"/>
+    <col min="478" max="478" width="29.42578125" bestFit="1" customWidth="1"/>
+    <col min="479" max="479" width="45" bestFit="1" customWidth="1"/>
+    <col min="480" max="480" width="34.5703125" bestFit="1" customWidth="1"/>
+    <col min="481" max="481" width="33.85546875" bestFit="1" customWidth="1"/>
+    <col min="482" max="482" width="39.85546875" bestFit="1" customWidth="1"/>
+    <col min="483" max="483" width="38.5703125" bestFit="1" customWidth="1"/>
+    <col min="484" max="484" width="48.42578125" bestFit="1" customWidth="1"/>
+    <col min="485" max="485" width="33.28515625" bestFit="1" customWidth="1"/>
+    <col min="486" max="486" width="31.28515625" bestFit="1" customWidth="1"/>
+    <col min="487" max="487" width="50.7109375" bestFit="1" customWidth="1"/>
+    <col min="488" max="488" width="29.5703125" bestFit="1" customWidth="1"/>
+    <col min="489" max="489" width="32.5703125" bestFit="1" customWidth="1"/>
+    <col min="490" max="490" width="29.5703125" bestFit="1" customWidth="1"/>
+    <col min="491" max="491" width="55.42578125" bestFit="1" customWidth="1"/>
+    <col min="492" max="492" width="33.28515625" bestFit="1" customWidth="1"/>
+    <col min="493" max="493" width="35" bestFit="1" customWidth="1"/>
+    <col min="494" max="494" width="34.140625" bestFit="1" customWidth="1"/>
+    <col min="495" max="495" width="27.28515625" bestFit="1" customWidth="1"/>
+    <col min="496" max="496" width="41.85546875" bestFit="1" customWidth="1"/>
+    <col min="497" max="497" width="32.5703125" bestFit="1" customWidth="1"/>
+    <col min="498" max="498" width="23.5703125" bestFit="1" customWidth="1"/>
+    <col min="499" max="499" width="49.85546875" bestFit="1" customWidth="1"/>
+    <col min="500" max="500" width="35.42578125" bestFit="1" customWidth="1"/>
+    <col min="501" max="501" width="30.7109375" bestFit="1" customWidth="1"/>
+    <col min="502" max="502" width="101.42578125" bestFit="1" customWidth="1"/>
+    <col min="503" max="503" width="66" bestFit="1" customWidth="1"/>
+    <col min="504" max="504" width="67.28515625" bestFit="1" customWidth="1"/>
+    <col min="505" max="505" width="59.140625" bestFit="1" customWidth="1"/>
+    <col min="506" max="506" width="51.140625" bestFit="1" customWidth="1"/>
+    <col min="507" max="507" width="31" bestFit="1" customWidth="1"/>
+    <col min="508" max="508" width="39.28515625" bestFit="1" customWidth="1"/>
+    <col min="509" max="509" width="17.140625" bestFit="1" customWidth="1"/>
+    <col min="510" max="510" width="17.5703125" bestFit="1" customWidth="1"/>
+    <col min="511" max="511" width="35.140625" bestFit="1" customWidth="1"/>
+    <col min="512" max="512" width="61.140625" bestFit="1" customWidth="1"/>
+    <col min="513" max="513" width="47.140625" bestFit="1" customWidth="1"/>
+    <col min="514" max="514" width="58.42578125" bestFit="1" customWidth="1"/>
+    <col min="515" max="515" width="38.85546875" bestFit="1" customWidth="1"/>
+    <col min="516" max="516" width="28" bestFit="1" customWidth="1"/>
+    <col min="517" max="517" width="44.5703125" bestFit="1" customWidth="1"/>
+    <col min="518" max="518" width="29.28515625" bestFit="1" customWidth="1"/>
+    <col min="519" max="519" width="37" bestFit="1" customWidth="1"/>
+    <col min="520" max="520" width="34.7109375" bestFit="1" customWidth="1"/>
+    <col min="521" max="521" width="39.5703125" bestFit="1" customWidth="1"/>
+    <col min="522" max="522" width="82.28515625" bestFit="1" customWidth="1"/>
+    <col min="523" max="523" width="52.7109375" bestFit="1" customWidth="1"/>
+    <col min="524" max="524" width="54.5703125" bestFit="1" customWidth="1"/>
+    <col min="525" max="525" width="30.28515625" bestFit="1" customWidth="1"/>
+    <col min="526" max="526" width="52.7109375" bestFit="1" customWidth="1"/>
+    <col min="527" max="527" width="18.7109375" bestFit="1" customWidth="1"/>
+    <col min="528" max="528" width="37.140625" bestFit="1" customWidth="1"/>
+    <col min="529" max="529" width="70.42578125" bestFit="1" customWidth="1"/>
+    <col min="530" max="530" width="63.5703125" bestFit="1" customWidth="1"/>
+    <col min="531" max="531" width="48.5703125" bestFit="1" customWidth="1"/>
+    <col min="532" max="532" width="66.7109375" bestFit="1" customWidth="1"/>
+    <col min="533" max="533" width="34.5703125" bestFit="1" customWidth="1"/>
+    <col min="534" max="534" width="50.42578125" bestFit="1" customWidth="1"/>
+    <col min="535" max="535" width="35" bestFit="1" customWidth="1"/>
+    <col min="536" max="536" width="58.85546875" bestFit="1" customWidth="1"/>
+    <col min="537" max="537" width="41.85546875" bestFit="1" customWidth="1"/>
+    <col min="538" max="538" width="53.85546875" bestFit="1" customWidth="1"/>
+    <col min="539" max="539" width="48.28515625" bestFit="1" customWidth="1"/>
+    <col min="540" max="540" width="44.140625" bestFit="1" customWidth="1"/>
+    <col min="541" max="541" width="40.28515625" bestFit="1" customWidth="1"/>
+    <col min="542" max="542" width="34.7109375" bestFit="1" customWidth="1"/>
+    <col min="543" max="543" width="32.7109375" bestFit="1" customWidth="1"/>
+    <col min="544" max="544" width="46.5703125" bestFit="1" customWidth="1"/>
+    <col min="545" max="545" width="74.28515625" bestFit="1" customWidth="1"/>
+    <col min="546" max="546" width="29.5703125" bestFit="1" customWidth="1"/>
+    <col min="547" max="547" width="55.42578125" bestFit="1" customWidth="1"/>
+    <col min="548" max="548" width="64.7109375" bestFit="1" customWidth="1"/>
+    <col min="549" max="549" width="57.42578125" bestFit="1" customWidth="1"/>
+    <col min="550" max="550" width="60.5703125" bestFit="1" customWidth="1"/>
+    <col min="551" max="551" width="44" bestFit="1" customWidth="1"/>
+    <col min="552" max="552" width="20" bestFit="1" customWidth="1"/>
+    <col min="553" max="553" width="49.28515625" bestFit="1" customWidth="1"/>
+    <col min="554" max="554" width="37" bestFit="1" customWidth="1"/>
+    <col min="555" max="555" width="66.42578125" bestFit="1" customWidth="1"/>
+    <col min="556" max="556" width="61.5703125" bestFit="1" customWidth="1"/>
+    <col min="557" max="557" width="37.28515625" bestFit="1" customWidth="1"/>
+    <col min="558" max="558" width="61.140625" bestFit="1" customWidth="1"/>
+    <col min="559" max="559" width="58.7109375" bestFit="1" customWidth="1"/>
+    <col min="560" max="560" width="70.28515625" bestFit="1" customWidth="1"/>
+    <col min="561" max="561" width="30.7109375" bestFit="1" customWidth="1"/>
+    <col min="562" max="562" width="60.85546875" bestFit="1" customWidth="1"/>
+    <col min="563" max="563" width="23.7109375" bestFit="1" customWidth="1"/>
+    <col min="564" max="564" width="43.140625" bestFit="1" customWidth="1"/>
+    <col min="565" max="565" width="34.7109375" bestFit="1" customWidth="1"/>
+    <col min="566" max="566" width="37" bestFit="1" customWidth="1"/>
+    <col min="567" max="567" width="55.85546875" bestFit="1" customWidth="1"/>
+    <col min="568" max="568" width="23.42578125" bestFit="1" customWidth="1"/>
+    <col min="569" max="569" width="46" bestFit="1" customWidth="1"/>
+    <col min="570" max="570" width="51.7109375" bestFit="1" customWidth="1"/>
+    <col min="571" max="571" width="51" bestFit="1" customWidth="1"/>
+    <col min="572" max="572" width="28.5703125" bestFit="1" customWidth="1"/>
+    <col min="573" max="573" width="61" bestFit="1" customWidth="1"/>
+    <col min="574" max="574" width="38.28515625" bestFit="1" customWidth="1"/>
+    <col min="575" max="575" width="76.140625" bestFit="1" customWidth="1"/>
+    <col min="576" max="576" width="53" bestFit="1" customWidth="1"/>
+    <col min="577" max="577" width="25" bestFit="1" customWidth="1"/>
+    <col min="578" max="578" width="41.140625" bestFit="1" customWidth="1"/>
+    <col min="579" max="579" width="17.85546875" bestFit="1" customWidth="1"/>
+    <col min="580" max="580" width="35.140625" bestFit="1" customWidth="1"/>
+    <col min="581" max="581" width="40" bestFit="1" customWidth="1"/>
+    <col min="582" max="582" width="54.7109375" bestFit="1" customWidth="1"/>
+    <col min="583" max="583" width="39.28515625" bestFit="1" customWidth="1"/>
+    <col min="584" max="584" width="35.7109375" bestFit="1" customWidth="1"/>
+    <col min="585" max="585" width="57.28515625" bestFit="1" customWidth="1"/>
+    <col min="586" max="586" width="49.42578125" bestFit="1" customWidth="1"/>
+    <col min="587" max="587" width="52.140625" bestFit="1" customWidth="1"/>
+    <col min="588" max="588" width="30.28515625" bestFit="1" customWidth="1"/>
+    <col min="589" max="589" width="58.28515625" bestFit="1" customWidth="1"/>
+    <col min="590" max="590" width="54.7109375" bestFit="1" customWidth="1"/>
+    <col min="591" max="591" width="54" bestFit="1" customWidth="1"/>
+    <col min="592" max="592" width="67.7109375" bestFit="1" customWidth="1"/>
+    <col min="593" max="593" width="54.140625" bestFit="1" customWidth="1"/>
+    <col min="594" max="594" width="59.42578125" bestFit="1" customWidth="1"/>
+    <col min="595" max="595" width="51.28515625" bestFit="1" customWidth="1"/>
+    <col min="596" max="596" width="53.5703125" bestFit="1" customWidth="1"/>
+    <col min="597" max="597" width="69.7109375" bestFit="1" customWidth="1"/>
+    <col min="598" max="598" width="41.42578125" bestFit="1" customWidth="1"/>
+    <col min="599" max="599" width="20.7109375" bestFit="1" customWidth="1"/>
+    <col min="600" max="600" width="45.85546875" bestFit="1" customWidth="1"/>
+    <col min="601" max="601" width="30" bestFit="1" customWidth="1"/>
+    <col min="602" max="603" width="27.28515625" bestFit="1" customWidth="1"/>
+    <col min="604" max="604" width="37.7109375" bestFit="1" customWidth="1"/>
+    <col min="605" max="605" width="18.85546875" bestFit="1" customWidth="1"/>
+    <col min="606" max="606" width="43.85546875" bestFit="1" customWidth="1"/>
+    <col min="607" max="607" width="38.28515625" bestFit="1" customWidth="1"/>
+    <col min="608" max="608" width="33.85546875" bestFit="1" customWidth="1"/>
+    <col min="609" max="609" width="45.5703125" bestFit="1" customWidth="1"/>
+    <col min="610" max="610" width="21" bestFit="1" customWidth="1"/>
+    <col min="611" max="611" width="17.5703125" bestFit="1" customWidth="1"/>
+    <col min="612" max="612" width="23.85546875" bestFit="1" customWidth="1"/>
+    <col min="613" max="613" width="24.28515625" bestFit="1" customWidth="1"/>
+    <col min="614" max="614" width="33.42578125" bestFit="1" customWidth="1"/>
+    <col min="615" max="615" width="13.140625" bestFit="1" customWidth="1"/>
+    <col min="616" max="616" width="20.28515625" bestFit="1" customWidth="1"/>
+    <col min="617" max="617" width="23.28515625" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:618">
@@ -20474,6 +21082,7 @@
       </c>
     </row>
   </sheetData>
+  <autoFilter ref="A2:WT2" xr:uid="{00000000-0001-0000-0000-000000000000}"/>
   <mergeCells count="1">
     <mergeCell ref="WP1:WS1"/>
   </mergeCells>
@@ -20484,17 +21093,612 @@
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0100-000000000000}">
   <dimension ref="A1:WT150"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="9.140625" defaultRowHeight="15"/>
   <cols>
-    <col min="469" max="469" width="24.85546875" customWidth="1"/>
+    <col min="1" max="1" width="10" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="18.85546875" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="24.28515625" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="10" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="17.42578125" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="52.140625" bestFit="1" customWidth="1"/>
+    <col min="7" max="8" width="18.42578125" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="18.7109375" bestFit="1" customWidth="1"/>
+    <col min="10" max="10" width="21.7109375" bestFit="1" customWidth="1"/>
+    <col min="11" max="11" width="23.85546875" bestFit="1" customWidth="1"/>
+    <col min="12" max="12" width="21.42578125" bestFit="1" customWidth="1"/>
+    <col min="13" max="13" width="31.5703125" bestFit="1" customWidth="1"/>
+    <col min="14" max="14" width="9" bestFit="1" customWidth="1"/>
+    <col min="15" max="15" width="38.5703125" bestFit="1" customWidth="1"/>
+    <col min="16" max="16" width="13.85546875" bestFit="1" customWidth="1"/>
+    <col min="17" max="17" width="9.28515625" bestFit="1" customWidth="1"/>
+    <col min="18" max="18" width="24.42578125" bestFit="1" customWidth="1"/>
+    <col min="19" max="20" width="47.7109375" bestFit="1" customWidth="1"/>
+    <col min="21" max="21" width="23" bestFit="1" customWidth="1"/>
+    <col min="22" max="22" width="53.5703125" bestFit="1" customWidth="1"/>
+    <col min="23" max="23" width="70.140625" bestFit="1" customWidth="1"/>
+    <col min="24" max="24" width="29.85546875" bestFit="1" customWidth="1"/>
+    <col min="25" max="25" width="47" bestFit="1" customWidth="1"/>
+    <col min="26" max="26" width="70.85546875" bestFit="1" customWidth="1"/>
+    <col min="27" max="27" width="18" bestFit="1" customWidth="1"/>
+    <col min="28" max="28" width="19.5703125" bestFit="1" customWidth="1"/>
+    <col min="29" max="29" width="18.5703125" bestFit="1" customWidth="1"/>
+    <col min="30" max="30" width="15.85546875" bestFit="1" customWidth="1"/>
+    <col min="31" max="31" width="18.42578125" bestFit="1" customWidth="1"/>
+    <col min="32" max="32" width="21.5703125" bestFit="1" customWidth="1"/>
+    <col min="33" max="33" width="17.5703125" bestFit="1" customWidth="1"/>
+    <col min="34" max="34" width="20.5703125" bestFit="1" customWidth="1"/>
+    <col min="35" max="35" width="19.140625" bestFit="1" customWidth="1"/>
+    <col min="36" max="36" width="57" bestFit="1" customWidth="1"/>
+    <col min="37" max="37" width="35" bestFit="1" customWidth="1"/>
+    <col min="38" max="38" width="21" bestFit="1" customWidth="1"/>
+    <col min="39" max="39" width="28.85546875" bestFit="1" customWidth="1"/>
+    <col min="40" max="40" width="58.28515625" bestFit="1" customWidth="1"/>
+    <col min="41" max="41" width="18.140625" bestFit="1" customWidth="1"/>
+    <col min="42" max="42" width="56" bestFit="1" customWidth="1"/>
+    <col min="43" max="43" width="36.140625" bestFit="1" customWidth="1"/>
+    <col min="44" max="44" width="29.28515625" bestFit="1" customWidth="1"/>
+    <col min="45" max="45" width="61.7109375" bestFit="1" customWidth="1"/>
+    <col min="46" max="46" width="28" bestFit="1" customWidth="1"/>
+    <col min="47" max="47" width="34.42578125" bestFit="1" customWidth="1"/>
+    <col min="48" max="48" width="37" bestFit="1" customWidth="1"/>
+    <col min="49" max="49" width="30.7109375" bestFit="1" customWidth="1"/>
+    <col min="50" max="50" width="22.5703125" bestFit="1" customWidth="1"/>
+    <col min="51" max="51" width="46" bestFit="1" customWidth="1"/>
+    <col min="52" max="52" width="54.7109375" bestFit="1" customWidth="1"/>
+    <col min="53" max="53" width="58.7109375" bestFit="1" customWidth="1"/>
+    <col min="54" max="54" width="43" bestFit="1" customWidth="1"/>
+    <col min="55" max="55" width="46" bestFit="1" customWidth="1"/>
+    <col min="56" max="56" width="54.7109375" bestFit="1" customWidth="1"/>
+    <col min="57" max="57" width="58.7109375" bestFit="1" customWidth="1"/>
+    <col min="58" max="58" width="43" bestFit="1" customWidth="1"/>
+    <col min="59" max="59" width="39.7109375" bestFit="1" customWidth="1"/>
+    <col min="60" max="60" width="55.5703125" bestFit="1" customWidth="1"/>
+    <col min="61" max="61" width="42.5703125" bestFit="1" customWidth="1"/>
+    <col min="62" max="62" width="39.5703125" bestFit="1" customWidth="1"/>
+    <col min="63" max="63" width="43.5703125" bestFit="1" customWidth="1"/>
+    <col min="64" max="64" width="30" bestFit="1" customWidth="1"/>
+    <col min="65" max="65" width="57" bestFit="1" customWidth="1"/>
+    <col min="66" max="66" width="21" bestFit="1" customWidth="1"/>
+    <col min="67" max="67" width="23.85546875" bestFit="1" customWidth="1"/>
+    <col min="68" max="68" width="50.42578125" bestFit="1" customWidth="1"/>
+    <col min="69" max="69" width="39.140625" bestFit="1" customWidth="1"/>
+    <col min="70" max="70" width="57.85546875" bestFit="1" customWidth="1"/>
+    <col min="71" max="71" width="45" bestFit="1" customWidth="1"/>
+    <col min="72" max="72" width="57.5703125" bestFit="1" customWidth="1"/>
+    <col min="73" max="73" width="61.7109375" bestFit="1" customWidth="1"/>
+    <col min="74" max="74" width="45.140625" bestFit="1" customWidth="1"/>
+    <col min="75" max="75" width="34.5703125" bestFit="1" customWidth="1"/>
+    <col min="76" max="76" width="42.140625" bestFit="1" customWidth="1"/>
+    <col min="77" max="77" width="47.7109375" bestFit="1" customWidth="1"/>
+    <col min="78" max="78" width="36.28515625" bestFit="1" customWidth="1"/>
+    <col min="79" max="79" width="42.85546875" bestFit="1" customWidth="1"/>
+    <col min="80" max="80" width="55.140625" bestFit="1" customWidth="1"/>
+    <col min="81" max="81" width="54.7109375" bestFit="1" customWidth="1"/>
+    <col min="82" max="82" width="54.5703125" bestFit="1" customWidth="1"/>
+    <col min="83" max="83" width="53.85546875" bestFit="1" customWidth="1"/>
+    <col min="84" max="84" width="44.140625" bestFit="1" customWidth="1"/>
+    <col min="85" max="85" width="52.28515625" bestFit="1" customWidth="1"/>
+    <col min="86" max="86" width="50.5703125" bestFit="1" customWidth="1"/>
+    <col min="87" max="87" width="40.140625" bestFit="1" customWidth="1"/>
+    <col min="88" max="88" width="35.42578125" bestFit="1" customWidth="1"/>
+    <col min="89" max="89" width="52.5703125" bestFit="1" customWidth="1"/>
+    <col min="90" max="90" width="51.7109375" bestFit="1" customWidth="1"/>
+    <col min="91" max="91" width="31.5703125" bestFit="1" customWidth="1"/>
+    <col min="92" max="92" width="33" bestFit="1" customWidth="1"/>
+    <col min="93" max="93" width="39.85546875" bestFit="1" customWidth="1"/>
+    <col min="94" max="94" width="53.28515625" bestFit="1" customWidth="1"/>
+    <col min="95" max="95" width="50.5703125" bestFit="1" customWidth="1"/>
+    <col min="96" max="96" width="60.85546875" bestFit="1" customWidth="1"/>
+    <col min="97" max="97" width="43" bestFit="1" customWidth="1"/>
+    <col min="98" max="98" width="53.5703125" bestFit="1" customWidth="1"/>
+    <col min="99" max="99" width="60.85546875" bestFit="1" customWidth="1"/>
+    <col min="100" max="100" width="26.85546875" bestFit="1" customWidth="1"/>
+    <col min="101" max="101" width="19.42578125" bestFit="1" customWidth="1"/>
+    <col min="102" max="102" width="56.42578125" bestFit="1" customWidth="1"/>
+    <col min="103" max="103" width="55.85546875" bestFit="1" customWidth="1"/>
+    <col min="104" max="104" width="28.85546875" bestFit="1" customWidth="1"/>
+    <col min="105" max="105" width="43.42578125" bestFit="1" customWidth="1"/>
+    <col min="106" max="106" width="31.5703125" bestFit="1" customWidth="1"/>
+    <col min="107" max="107" width="39" bestFit="1" customWidth="1"/>
+    <col min="108" max="108" width="32.140625" bestFit="1" customWidth="1"/>
+    <col min="109" max="109" width="54.28515625" bestFit="1" customWidth="1"/>
+    <col min="110" max="110" width="52.5703125" bestFit="1" customWidth="1"/>
+    <col min="111" max="111" width="37.7109375" bestFit="1" customWidth="1"/>
+    <col min="112" max="112" width="30.42578125" bestFit="1" customWidth="1"/>
+    <col min="113" max="113" width="30.7109375" bestFit="1" customWidth="1"/>
+    <col min="114" max="114" width="56.42578125" bestFit="1" customWidth="1"/>
+    <col min="115" max="115" width="59.28515625" bestFit="1" customWidth="1"/>
+    <col min="116" max="116" width="23.140625" bestFit="1" customWidth="1"/>
+    <col min="117" max="117" width="56.7109375" bestFit="1" customWidth="1"/>
+    <col min="118" max="118" width="42.85546875" bestFit="1" customWidth="1"/>
+    <col min="119" max="119" width="21" bestFit="1" customWidth="1"/>
+    <col min="120" max="120" width="50.7109375" bestFit="1" customWidth="1"/>
+    <col min="121" max="121" width="58.42578125" bestFit="1" customWidth="1"/>
+    <col min="122" max="122" width="32.5703125" bestFit="1" customWidth="1"/>
+    <col min="123" max="123" width="38.28515625" bestFit="1" customWidth="1"/>
+    <col min="124" max="124" width="47.28515625" bestFit="1" customWidth="1"/>
+    <col min="125" max="125" width="43.7109375" bestFit="1" customWidth="1"/>
+    <col min="126" max="126" width="44" bestFit="1" customWidth="1"/>
+    <col min="127" max="127" width="29" bestFit="1" customWidth="1"/>
+    <col min="128" max="128" width="29.28515625" bestFit="1" customWidth="1"/>
+    <col min="129" max="129" width="33.28515625" bestFit="1" customWidth="1"/>
+    <col min="130" max="130" width="18.85546875" bestFit="1" customWidth="1"/>
+    <col min="131" max="131" width="51.28515625" bestFit="1" customWidth="1"/>
+    <col min="132" max="132" width="56.42578125" bestFit="1" customWidth="1"/>
+    <col min="133" max="133" width="55" bestFit="1" customWidth="1"/>
+    <col min="134" max="134" width="53.85546875" bestFit="1" customWidth="1"/>
+    <col min="135" max="135" width="29.7109375" bestFit="1" customWidth="1"/>
+    <col min="136" max="136" width="19.85546875" bestFit="1" customWidth="1"/>
+    <col min="137" max="137" width="41" bestFit="1" customWidth="1"/>
+    <col min="138" max="138" width="30.28515625" bestFit="1" customWidth="1"/>
+    <col min="139" max="139" width="39.85546875" bestFit="1" customWidth="1"/>
+    <col min="140" max="140" width="58.85546875" bestFit="1" customWidth="1"/>
+    <col min="141" max="141" width="39" bestFit="1" customWidth="1"/>
+    <col min="142" max="142" width="27.42578125" bestFit="1" customWidth="1"/>
+    <col min="143" max="143" width="37.42578125" bestFit="1" customWidth="1"/>
+    <col min="144" max="144" width="53.140625" bestFit="1" customWidth="1"/>
+    <col min="145" max="145" width="37.42578125" bestFit="1" customWidth="1"/>
+    <col min="146" max="146" width="28.85546875" bestFit="1" customWidth="1"/>
+    <col min="147" max="147" width="47" bestFit="1" customWidth="1"/>
+    <col min="148" max="148" width="39.5703125" bestFit="1" customWidth="1"/>
+    <col min="149" max="149" width="40.42578125" bestFit="1" customWidth="1"/>
+    <col min="150" max="150" width="44.5703125" bestFit="1" customWidth="1"/>
+    <col min="151" max="151" width="32.28515625" bestFit="1" customWidth="1"/>
+    <col min="152" max="152" width="49" bestFit="1" customWidth="1"/>
+    <col min="153" max="153" width="44.42578125" bestFit="1" customWidth="1"/>
+    <col min="154" max="154" width="48.7109375" bestFit="1" customWidth="1"/>
+    <col min="155" max="155" width="54.85546875" bestFit="1" customWidth="1"/>
+    <col min="156" max="156" width="51.7109375" bestFit="1" customWidth="1"/>
+    <col min="157" max="157" width="48.7109375" bestFit="1" customWidth="1"/>
+    <col min="158" max="158" width="46.140625" bestFit="1" customWidth="1"/>
+    <col min="159" max="159" width="33.5703125" bestFit="1" customWidth="1"/>
+    <col min="160" max="160" width="32.28515625" bestFit="1" customWidth="1"/>
+    <col min="161" max="161" width="53.7109375" bestFit="1" customWidth="1"/>
+    <col min="162" max="162" width="48.7109375" bestFit="1" customWidth="1"/>
+    <col min="163" max="163" width="56.28515625" bestFit="1" customWidth="1"/>
+    <col min="164" max="164" width="51.28515625" bestFit="1" customWidth="1"/>
+    <col min="165" max="165" width="61.28515625" bestFit="1" customWidth="1"/>
+    <col min="166" max="166" width="59.5703125" bestFit="1" customWidth="1"/>
+    <col min="167" max="167" width="56.85546875" bestFit="1" customWidth="1"/>
+    <col min="168" max="169" width="57.42578125" bestFit="1" customWidth="1"/>
+    <col min="170" max="170" width="34.85546875" bestFit="1" customWidth="1"/>
+    <col min="171" max="171" width="32.140625" bestFit="1" customWidth="1"/>
+    <col min="172" max="172" width="40.42578125" bestFit="1" customWidth="1"/>
+    <col min="173" max="173" width="21.85546875" bestFit="1" customWidth="1"/>
+    <col min="174" max="174" width="20.5703125" bestFit="1" customWidth="1"/>
+    <col min="175" max="175" width="66.85546875" bestFit="1" customWidth="1"/>
+    <col min="176" max="176" width="58.140625" bestFit="1" customWidth="1"/>
+    <col min="177" max="177" width="56" bestFit="1" customWidth="1"/>
+    <col min="178" max="178" width="42.42578125" bestFit="1" customWidth="1"/>
+    <col min="179" max="179" width="49.28515625" bestFit="1" customWidth="1"/>
+    <col min="180" max="180" width="55.5703125" bestFit="1" customWidth="1"/>
+    <col min="181" max="181" width="29.5703125" bestFit="1" customWidth="1"/>
+    <col min="182" max="182" width="41.85546875" bestFit="1" customWidth="1"/>
+    <col min="183" max="183" width="50.5703125" bestFit="1" customWidth="1"/>
+    <col min="184" max="184" width="42.7109375" bestFit="1" customWidth="1"/>
+    <col min="185" max="185" width="56.140625" bestFit="1" customWidth="1"/>
+    <col min="186" max="186" width="25" bestFit="1" customWidth="1"/>
+    <col min="187" max="187" width="60" bestFit="1" customWidth="1"/>
+    <col min="188" max="188" width="50.7109375" bestFit="1" customWidth="1"/>
+    <col min="189" max="189" width="80.28515625" bestFit="1" customWidth="1"/>
+    <col min="190" max="190" width="41.28515625" bestFit="1" customWidth="1"/>
+    <col min="191" max="191" width="52.28515625" bestFit="1" customWidth="1"/>
+    <col min="192" max="192" width="36.28515625" bestFit="1" customWidth="1"/>
+    <col min="193" max="193" width="58.42578125" bestFit="1" customWidth="1"/>
+    <col min="194" max="194" width="50.42578125" bestFit="1" customWidth="1"/>
+    <col min="195" max="195" width="49.5703125" bestFit="1" customWidth="1"/>
+    <col min="196" max="196" width="60.85546875" bestFit="1" customWidth="1"/>
+    <col min="197" max="197" width="54.5703125" bestFit="1" customWidth="1"/>
+    <col min="198" max="198" width="55.85546875" bestFit="1" customWidth="1"/>
+    <col min="199" max="199" width="58.85546875" bestFit="1" customWidth="1"/>
+    <col min="200" max="200" width="43.85546875" bestFit="1" customWidth="1"/>
+    <col min="201" max="201" width="49.5703125" bestFit="1" customWidth="1"/>
+    <col min="202" max="202" width="30.42578125" bestFit="1" customWidth="1"/>
+    <col min="203" max="203" width="32.7109375" bestFit="1" customWidth="1"/>
+    <col min="204" max="204" width="46.5703125" bestFit="1" customWidth="1"/>
+    <col min="205" max="205" width="50.7109375" bestFit="1" customWidth="1"/>
+    <col min="206" max="206" width="37.5703125" bestFit="1" customWidth="1"/>
+    <col min="207" max="207" width="51.140625" bestFit="1" customWidth="1"/>
+    <col min="208" max="208" width="40.28515625" bestFit="1" customWidth="1"/>
+    <col min="209" max="209" width="55" bestFit="1" customWidth="1"/>
+    <col min="210" max="210" width="54.140625" bestFit="1" customWidth="1"/>
+    <col min="211" max="211" width="35.28515625" bestFit="1" customWidth="1"/>
+    <col min="212" max="212" width="41.140625" bestFit="1" customWidth="1"/>
+    <col min="213" max="213" width="54.140625" bestFit="1" customWidth="1"/>
+    <col min="214" max="214" width="57" bestFit="1" customWidth="1"/>
+    <col min="215" max="215" width="56.140625" bestFit="1" customWidth="1"/>
+    <col min="216" max="216" width="47" bestFit="1" customWidth="1"/>
+    <col min="217" max="217" width="37.5703125" bestFit="1" customWidth="1"/>
+    <col min="218" max="218" width="30.140625" bestFit="1" customWidth="1"/>
+    <col min="219" max="219" width="49.7109375" bestFit="1" customWidth="1"/>
+    <col min="220" max="220" width="46.28515625" bestFit="1" customWidth="1"/>
+    <col min="221" max="221" width="56.140625" bestFit="1" customWidth="1"/>
+    <col min="222" max="222" width="39.28515625" bestFit="1" customWidth="1"/>
+    <col min="223" max="223" width="44.85546875" bestFit="1" customWidth="1"/>
+    <col min="224" max="224" width="49.140625" bestFit="1" customWidth="1"/>
+    <col min="225" max="225" width="45.42578125" bestFit="1" customWidth="1"/>
+    <col min="226" max="226" width="44.85546875" bestFit="1" customWidth="1"/>
+    <col min="227" max="227" width="55" bestFit="1" customWidth="1"/>
+    <col min="228" max="228" width="43.5703125" bestFit="1" customWidth="1"/>
+    <col min="229" max="229" width="38.85546875" bestFit="1" customWidth="1"/>
+    <col min="230" max="230" width="56.5703125" bestFit="1" customWidth="1"/>
+    <col min="231" max="231" width="33.5703125" bestFit="1" customWidth="1"/>
+    <col min="232" max="232" width="47.28515625" bestFit="1" customWidth="1"/>
+    <col min="233" max="233" width="59.28515625" bestFit="1" customWidth="1"/>
+    <col min="234" max="234" width="13.85546875" bestFit="1" customWidth="1"/>
+    <col min="235" max="235" width="30.7109375" bestFit="1" customWidth="1"/>
+    <col min="236" max="236" width="26" bestFit="1" customWidth="1"/>
+    <col min="237" max="237" width="25.140625" bestFit="1" customWidth="1"/>
+    <col min="238" max="238" width="67" bestFit="1" customWidth="1"/>
+    <col min="239" max="239" width="52.42578125" bestFit="1" customWidth="1"/>
+    <col min="240" max="240" width="50.5703125" bestFit="1" customWidth="1"/>
+    <col min="241" max="241" width="51" bestFit="1" customWidth="1"/>
+    <col min="242" max="242" width="47.85546875" bestFit="1" customWidth="1"/>
+    <col min="243" max="243" width="42.7109375" bestFit="1" customWidth="1"/>
+    <col min="244" max="244" width="55" bestFit="1" customWidth="1"/>
+    <col min="245" max="245" width="50" bestFit="1" customWidth="1"/>
+    <col min="246" max="246" width="46.140625" bestFit="1" customWidth="1"/>
+    <col min="247" max="247" width="52.5703125" bestFit="1" customWidth="1"/>
+    <col min="248" max="248" width="44.140625" bestFit="1" customWidth="1"/>
+    <col min="249" max="249" width="33" bestFit="1" customWidth="1"/>
+    <col min="250" max="250" width="38.5703125" bestFit="1" customWidth="1"/>
+    <col min="251" max="251" width="48.85546875" bestFit="1" customWidth="1"/>
+    <col min="252" max="252" width="47.5703125" bestFit="1" customWidth="1"/>
+    <col min="253" max="253" width="13.140625" bestFit="1" customWidth="1"/>
+    <col min="254" max="254" width="31" bestFit="1" customWidth="1"/>
+    <col min="255" max="255" width="38.7109375" bestFit="1" customWidth="1"/>
+    <col min="256" max="256" width="31.85546875" bestFit="1" customWidth="1"/>
+    <col min="257" max="257" width="31.28515625" bestFit="1" customWidth="1"/>
+    <col min="258" max="258" width="58.42578125" bestFit="1" customWidth="1"/>
+    <col min="259" max="259" width="40" bestFit="1" customWidth="1"/>
+    <col min="260" max="260" width="24.28515625" bestFit="1" customWidth="1"/>
+    <col min="261" max="261" width="24.140625" bestFit="1" customWidth="1"/>
+    <col min="262" max="262" width="27.5703125" bestFit="1" customWidth="1"/>
+    <col min="263" max="263" width="36.140625" bestFit="1" customWidth="1"/>
+    <col min="264" max="264" width="36" bestFit="1" customWidth="1"/>
+    <col min="265" max="265" width="21.42578125" bestFit="1" customWidth="1"/>
+    <col min="266" max="266" width="18.42578125" bestFit="1" customWidth="1"/>
+    <col min="267" max="267" width="29.5703125" bestFit="1" customWidth="1"/>
+    <col min="268" max="268" width="61.85546875" bestFit="1" customWidth="1"/>
+    <col min="269" max="269" width="22.140625" bestFit="1" customWidth="1"/>
+    <col min="270" max="270" width="57" bestFit="1" customWidth="1"/>
+    <col min="271" max="271" width="56.140625" bestFit="1" customWidth="1"/>
+    <col min="272" max="272" width="29.140625" bestFit="1" customWidth="1"/>
+    <col min="273" max="273" width="21.42578125" bestFit="1" customWidth="1"/>
+    <col min="274" max="274" width="38.140625" bestFit="1" customWidth="1"/>
+    <col min="275" max="275" width="19.140625" bestFit="1" customWidth="1"/>
+    <col min="276" max="276" width="27.85546875" bestFit="1" customWidth="1"/>
+    <col min="277" max="277" width="57.7109375" bestFit="1" customWidth="1"/>
+    <col min="278" max="278" width="25.28515625" bestFit="1" customWidth="1"/>
+    <col min="279" max="279" width="36.7109375" bestFit="1" customWidth="1"/>
+    <col min="280" max="280" width="52.7109375" bestFit="1" customWidth="1"/>
+    <col min="281" max="281" width="13.42578125" bestFit="1" customWidth="1"/>
+    <col min="282" max="282" width="56.7109375" bestFit="1" customWidth="1"/>
+    <col min="283" max="283" width="52.7109375" bestFit="1" customWidth="1"/>
+    <col min="284" max="284" width="22.7109375" bestFit="1" customWidth="1"/>
+    <col min="285" max="285" width="40.42578125" bestFit="1" customWidth="1"/>
+    <col min="286" max="286" width="39.5703125" bestFit="1" customWidth="1"/>
+    <col min="287" max="287" width="25" bestFit="1" customWidth="1"/>
+    <col min="288" max="288" width="53.28515625" bestFit="1" customWidth="1"/>
+    <col min="289" max="289" width="66.85546875" bestFit="1" customWidth="1"/>
+    <col min="290" max="290" width="30.5703125" bestFit="1" customWidth="1"/>
+    <col min="291" max="291" width="29.85546875" bestFit="1" customWidth="1"/>
+    <col min="292" max="292" width="19.5703125" bestFit="1" customWidth="1"/>
+    <col min="293" max="293" width="38" bestFit="1" customWidth="1"/>
+    <col min="294" max="294" width="24.5703125" bestFit="1" customWidth="1"/>
+    <col min="295" max="295" width="19.28515625" bestFit="1" customWidth="1"/>
+    <col min="296" max="296" width="23.85546875" bestFit="1" customWidth="1"/>
+    <col min="297" max="297" width="30.7109375" bestFit="1" customWidth="1"/>
+    <col min="298" max="298" width="28.28515625" bestFit="1" customWidth="1"/>
+    <col min="299" max="299" width="54.42578125" bestFit="1" customWidth="1"/>
+    <col min="300" max="300" width="40" bestFit="1" customWidth="1"/>
+    <col min="301" max="301" width="40.42578125" bestFit="1" customWidth="1"/>
+    <col min="302" max="302" width="37" bestFit="1" customWidth="1"/>
+    <col min="303" max="303" width="11.85546875" bestFit="1" customWidth="1"/>
+    <col min="304" max="304" width="45" bestFit="1" customWidth="1"/>
+    <col min="305" max="305" width="43.7109375" bestFit="1" customWidth="1"/>
+    <col min="306" max="306" width="21" bestFit="1" customWidth="1"/>
+    <col min="307" max="307" width="54.85546875" bestFit="1" customWidth="1"/>
+    <col min="308" max="308" width="43.28515625" bestFit="1" customWidth="1"/>
+    <col min="309" max="309" width="29" bestFit="1" customWidth="1"/>
+    <col min="310" max="310" width="40.85546875" bestFit="1" customWidth="1"/>
+    <col min="311" max="311" width="50.140625" bestFit="1" customWidth="1"/>
+    <col min="312" max="312" width="53.140625" bestFit="1" customWidth="1"/>
+    <col min="313" max="313" width="42.5703125" bestFit="1" customWidth="1"/>
+    <col min="314" max="314" width="39.85546875" bestFit="1" customWidth="1"/>
+    <col min="315" max="315" width="34.42578125" bestFit="1" customWidth="1"/>
+    <col min="316" max="316" width="44.5703125" bestFit="1" customWidth="1"/>
+    <col min="317" max="317" width="47.140625" bestFit="1" customWidth="1"/>
+    <col min="318" max="318" width="18.28515625" bestFit="1" customWidth="1"/>
+    <col min="319" max="319" width="25" bestFit="1" customWidth="1"/>
+    <col min="320" max="320" width="56.42578125" bestFit="1" customWidth="1"/>
+    <col min="321" max="321" width="28.85546875" bestFit="1" customWidth="1"/>
+    <col min="322" max="322" width="21" bestFit="1" customWidth="1"/>
+    <col min="323" max="323" width="38.28515625" bestFit="1" customWidth="1"/>
+    <col min="324" max="324" width="24.42578125" bestFit="1" customWidth="1"/>
+    <col min="325" max="325" width="18.85546875" bestFit="1" customWidth="1"/>
+    <col min="326" max="326" width="30.28515625" bestFit="1" customWidth="1"/>
+    <col min="327" max="327" width="32.7109375" bestFit="1" customWidth="1"/>
+    <col min="328" max="328" width="29.7109375" bestFit="1" customWidth="1"/>
+    <col min="329" max="329" width="56" bestFit="1" customWidth="1"/>
+    <col min="330" max="330" width="49.5703125" bestFit="1" customWidth="1"/>
+    <col min="331" max="331" width="44.5703125" bestFit="1" customWidth="1"/>
+    <col min="332" max="332" width="24.140625" bestFit="1" customWidth="1"/>
+    <col min="333" max="333" width="30.5703125" bestFit="1" customWidth="1"/>
+    <col min="334" max="334" width="30.7109375" bestFit="1" customWidth="1"/>
+    <col min="335" max="335" width="45" bestFit="1" customWidth="1"/>
+    <col min="336" max="336" width="49.5703125" bestFit="1" customWidth="1"/>
+    <col min="337" max="337" width="49.28515625" bestFit="1" customWidth="1"/>
+    <col min="338" max="338" width="44.85546875" bestFit="1" customWidth="1"/>
+    <col min="339" max="339" width="51" bestFit="1" customWidth="1"/>
+    <col min="340" max="340" width="52.5703125" bestFit="1" customWidth="1"/>
+    <col min="341" max="341" width="39.28515625" bestFit="1" customWidth="1"/>
+    <col min="342" max="342" width="44.42578125" bestFit="1" customWidth="1"/>
+    <col min="343" max="343" width="22.28515625" bestFit="1" customWidth="1"/>
+    <col min="344" max="344" width="55.28515625" bestFit="1" customWidth="1"/>
+    <col min="345" max="345" width="55.85546875" bestFit="1" customWidth="1"/>
+    <col min="346" max="346" width="44" bestFit="1" customWidth="1"/>
+    <col min="347" max="350" width="33.7109375" bestFit="1" customWidth="1"/>
+    <col min="351" max="351" width="51.7109375" bestFit="1" customWidth="1"/>
+    <col min="352" max="352" width="24.85546875" bestFit="1" customWidth="1"/>
+    <col min="353" max="353" width="27.7109375" bestFit="1" customWidth="1"/>
+    <col min="354" max="354" width="56.5703125" bestFit="1" customWidth="1"/>
+    <col min="355" max="355" width="55.140625" bestFit="1" customWidth="1"/>
+    <col min="356" max="356" width="57.28515625" bestFit="1" customWidth="1"/>
+    <col min="357" max="357" width="56.5703125" bestFit="1" customWidth="1"/>
+    <col min="358" max="358" width="56" bestFit="1" customWidth="1"/>
+    <col min="359" max="359" width="46.140625" bestFit="1" customWidth="1"/>
+    <col min="360" max="360" width="47.28515625" bestFit="1" customWidth="1"/>
+    <col min="361" max="361" width="33.85546875" bestFit="1" customWidth="1"/>
+    <col min="362" max="362" width="21.85546875" bestFit="1" customWidth="1"/>
+    <col min="363" max="363" width="49.42578125" bestFit="1" customWidth="1"/>
+    <col min="364" max="364" width="56.140625" bestFit="1" customWidth="1"/>
+    <col min="365" max="365" width="33.140625" bestFit="1" customWidth="1"/>
+    <col min="366" max="366" width="25.140625" bestFit="1" customWidth="1"/>
+    <col min="367" max="367" width="29" bestFit="1" customWidth="1"/>
+    <col min="368" max="368" width="29.7109375" bestFit="1" customWidth="1"/>
+    <col min="369" max="369" width="33.42578125" bestFit="1" customWidth="1"/>
+    <col min="370" max="370" width="32.28515625" bestFit="1" customWidth="1"/>
+    <col min="371" max="371" width="35.5703125" bestFit="1" customWidth="1"/>
+    <col min="372" max="372" width="42.7109375" bestFit="1" customWidth="1"/>
+    <col min="373" max="373" width="63" bestFit="1" customWidth="1"/>
+    <col min="374" max="374" width="21.7109375" bestFit="1" customWidth="1"/>
+    <col min="375" max="375" width="56.7109375" bestFit="1" customWidth="1"/>
+    <col min="376" max="376" width="40.5703125" bestFit="1" customWidth="1"/>
+    <col min="377" max="377" width="56" bestFit="1" customWidth="1"/>
+    <col min="378" max="378" width="40.5703125" bestFit="1" customWidth="1"/>
+    <col min="379" max="379" width="61.140625" bestFit="1" customWidth="1"/>
+    <col min="380" max="380" width="30.85546875" bestFit="1" customWidth="1"/>
+    <col min="381" max="381" width="56.7109375" bestFit="1" customWidth="1"/>
+    <col min="382" max="382" width="100" bestFit="1" customWidth="1"/>
+    <col min="383" max="383" width="32.42578125" bestFit="1" customWidth="1"/>
+    <col min="384" max="384" width="54" bestFit="1" customWidth="1"/>
+    <col min="385" max="385" width="43.7109375" bestFit="1" customWidth="1"/>
+    <col min="386" max="386" width="36" bestFit="1" customWidth="1"/>
+    <col min="387" max="387" width="60.140625" bestFit="1" customWidth="1"/>
+    <col min="388" max="388" width="35.5703125" bestFit="1" customWidth="1"/>
+    <col min="389" max="389" width="50.28515625" bestFit="1" customWidth="1"/>
+    <col min="390" max="390" width="39.28515625" bestFit="1" customWidth="1"/>
+    <col min="391" max="391" width="20.7109375" bestFit="1" customWidth="1"/>
+    <col min="392" max="392" width="20.28515625" bestFit="1" customWidth="1"/>
+    <col min="393" max="393" width="54.28515625" bestFit="1" customWidth="1"/>
+    <col min="394" max="394" width="30.85546875" bestFit="1" customWidth="1"/>
+    <col min="395" max="395" width="36.85546875" bestFit="1" customWidth="1"/>
+    <col min="396" max="396" width="29.42578125" bestFit="1" customWidth="1"/>
+    <col min="397" max="397" width="62.140625" bestFit="1" customWidth="1"/>
+    <col min="398" max="398" width="34.7109375" bestFit="1" customWidth="1"/>
+    <col min="399" max="399" width="35" bestFit="1" customWidth="1"/>
+    <col min="400" max="400" width="59.28515625" bestFit="1" customWidth="1"/>
+    <col min="401" max="401" width="49.140625" bestFit="1" customWidth="1"/>
+    <col min="402" max="402" width="27.140625" bestFit="1" customWidth="1"/>
+    <col min="403" max="403" width="56.85546875" bestFit="1" customWidth="1"/>
+    <col min="404" max="404" width="43.42578125" bestFit="1" customWidth="1"/>
+    <col min="405" max="405" width="37.85546875" bestFit="1" customWidth="1"/>
+    <col min="406" max="406" width="27.28515625" bestFit="1" customWidth="1"/>
+    <col min="407" max="407" width="40.85546875" bestFit="1" customWidth="1"/>
+    <col min="408" max="408" width="49.28515625" bestFit="1" customWidth="1"/>
+    <col min="409" max="410" width="49" bestFit="1" customWidth="1"/>
+    <col min="411" max="411" width="40.5703125" bestFit="1" customWidth="1"/>
+    <col min="412" max="412" width="39.28515625" bestFit="1" customWidth="1"/>
+    <col min="413" max="413" width="51.5703125" bestFit="1" customWidth="1"/>
+    <col min="414" max="414" width="41.5703125" bestFit="1" customWidth="1"/>
+    <col min="415" max="415" width="38.42578125" bestFit="1" customWidth="1"/>
+    <col min="416" max="416" width="44.5703125" bestFit="1" customWidth="1"/>
+    <col min="417" max="417" width="34.85546875" bestFit="1" customWidth="1"/>
+    <col min="418" max="418" width="46.28515625" bestFit="1" customWidth="1"/>
+    <col min="419" max="419" width="40.85546875" bestFit="1" customWidth="1"/>
+    <col min="420" max="420" width="56.28515625" bestFit="1" customWidth="1"/>
+    <col min="421" max="421" width="49.85546875" bestFit="1" customWidth="1"/>
+    <col min="422" max="422" width="63.42578125" bestFit="1" customWidth="1"/>
+    <col min="423" max="423" width="55.85546875" bestFit="1" customWidth="1"/>
+    <col min="424" max="424" width="54.28515625" bestFit="1" customWidth="1"/>
+    <col min="425" max="425" width="38.85546875" bestFit="1" customWidth="1"/>
+    <col min="426" max="426" width="51.140625" bestFit="1" customWidth="1"/>
+    <col min="427" max="427" width="53.28515625" bestFit="1" customWidth="1"/>
+    <col min="428" max="428" width="40.28515625" bestFit="1" customWidth="1"/>
+    <col min="429" max="429" width="36.28515625" bestFit="1" customWidth="1"/>
+    <col min="430" max="430" width="43.28515625" bestFit="1" customWidth="1"/>
+    <col min="431" max="431" width="58.42578125" bestFit="1" customWidth="1"/>
+    <col min="432" max="432" width="43.7109375" bestFit="1" customWidth="1"/>
+    <col min="433" max="433" width="31.140625" bestFit="1" customWidth="1"/>
+    <col min="434" max="434" width="59.7109375" bestFit="1" customWidth="1"/>
+    <col min="435" max="435" width="58.140625" bestFit="1" customWidth="1"/>
+    <col min="436" max="436" width="59.7109375" bestFit="1" customWidth="1"/>
+    <col min="437" max="437" width="29.28515625" bestFit="1" customWidth="1"/>
+    <col min="438" max="438" width="29.85546875" bestFit="1" customWidth="1"/>
+    <col min="439" max="439" width="43.7109375" bestFit="1" customWidth="1"/>
+    <col min="440" max="440" width="21.5703125" bestFit="1" customWidth="1"/>
+    <col min="441" max="441" width="26.7109375" bestFit="1" customWidth="1"/>
+    <col min="442" max="442" width="37.7109375" bestFit="1" customWidth="1"/>
+    <col min="443" max="443" width="22.42578125" bestFit="1" customWidth="1"/>
+    <col min="444" max="444" width="18.7109375" bestFit="1" customWidth="1"/>
+    <col min="445" max="445" width="37.7109375" bestFit="1" customWidth="1"/>
+    <col min="446" max="446" width="32.5703125" bestFit="1" customWidth="1"/>
+    <col min="447" max="447" width="29.140625" bestFit="1" customWidth="1"/>
+    <col min="448" max="448" width="56" bestFit="1" customWidth="1"/>
+    <col min="449" max="449" width="21.7109375" bestFit="1" customWidth="1"/>
+    <col min="450" max="450" width="22.7109375" bestFit="1" customWidth="1"/>
+    <col min="451" max="451" width="33" bestFit="1" customWidth="1"/>
+    <col min="452" max="452" width="36" bestFit="1" customWidth="1"/>
+    <col min="453" max="453" width="19.7109375" bestFit="1" customWidth="1"/>
+    <col min="454" max="454" width="24.5703125" bestFit="1" customWidth="1"/>
+    <col min="455" max="455" width="24.7109375" bestFit="1" customWidth="1"/>
+    <col min="456" max="456" width="48.42578125" bestFit="1" customWidth="1"/>
+    <col min="457" max="457" width="32" bestFit="1" customWidth="1"/>
+    <col min="458" max="459" width="37.5703125" bestFit="1" customWidth="1"/>
+    <col min="460" max="460" width="25.140625" bestFit="1" customWidth="1"/>
+    <col min="461" max="462" width="33.28515625" bestFit="1" customWidth="1"/>
+    <col min="463" max="463" width="28.85546875" bestFit="1" customWidth="1"/>
+    <col min="464" max="466" width="26" bestFit="1" customWidth="1"/>
+    <col min="467" max="468" width="33.140625" bestFit="1" customWidth="1"/>
+    <col min="469" max="469" width="38.5703125" bestFit="1" customWidth="1"/>
+    <col min="470" max="472" width="38.28515625" bestFit="1" customWidth="1"/>
+    <col min="473" max="473" width="37.140625" bestFit="1" customWidth="1"/>
+    <col min="474" max="474" width="36.85546875" bestFit="1" customWidth="1"/>
+    <col min="475" max="475" width="46.140625" bestFit="1" customWidth="1"/>
+    <col min="476" max="476" width="33.28515625" bestFit="1" customWidth="1"/>
+    <col min="477" max="477" width="26.7109375" bestFit="1" customWidth="1"/>
+    <col min="478" max="478" width="29.42578125" bestFit="1" customWidth="1"/>
+    <col min="479" max="479" width="45" bestFit="1" customWidth="1"/>
+    <col min="480" max="480" width="34.5703125" bestFit="1" customWidth="1"/>
+    <col min="481" max="481" width="33.85546875" bestFit="1" customWidth="1"/>
+    <col min="482" max="482" width="39.85546875" bestFit="1" customWidth="1"/>
+    <col min="483" max="483" width="38.5703125" bestFit="1" customWidth="1"/>
+    <col min="484" max="484" width="48.42578125" bestFit="1" customWidth="1"/>
+    <col min="485" max="485" width="33.28515625" bestFit="1" customWidth="1"/>
+    <col min="486" max="486" width="31.28515625" bestFit="1" customWidth="1"/>
+    <col min="487" max="487" width="50.7109375" bestFit="1" customWidth="1"/>
+    <col min="488" max="488" width="29.5703125" bestFit="1" customWidth="1"/>
+    <col min="489" max="489" width="32.5703125" bestFit="1" customWidth="1"/>
+    <col min="490" max="490" width="29.5703125" bestFit="1" customWidth="1"/>
+    <col min="491" max="491" width="55.42578125" bestFit="1" customWidth="1"/>
+    <col min="492" max="492" width="33.28515625" bestFit="1" customWidth="1"/>
+    <col min="493" max="493" width="35" bestFit="1" customWidth="1"/>
+    <col min="494" max="494" width="34.140625" bestFit="1" customWidth="1"/>
+    <col min="495" max="495" width="27.28515625" bestFit="1" customWidth="1"/>
+    <col min="496" max="496" width="41.85546875" bestFit="1" customWidth="1"/>
+    <col min="497" max="497" width="32.5703125" bestFit="1" customWidth="1"/>
+    <col min="498" max="498" width="23.5703125" bestFit="1" customWidth="1"/>
+    <col min="499" max="499" width="49.85546875" bestFit="1" customWidth="1"/>
+    <col min="500" max="500" width="35.42578125" bestFit="1" customWidth="1"/>
+    <col min="501" max="501" width="30.7109375" bestFit="1" customWidth="1"/>
+    <col min="502" max="502" width="101.42578125" bestFit="1" customWidth="1"/>
+    <col min="503" max="503" width="66" bestFit="1" customWidth="1"/>
+    <col min="504" max="504" width="67.28515625" bestFit="1" customWidth="1"/>
+    <col min="505" max="505" width="59.140625" bestFit="1" customWidth="1"/>
+    <col min="506" max="506" width="51.140625" bestFit="1" customWidth="1"/>
+    <col min="507" max="507" width="31" bestFit="1" customWidth="1"/>
+    <col min="508" max="508" width="39.28515625" bestFit="1" customWidth="1"/>
+    <col min="509" max="509" width="17.140625" bestFit="1" customWidth="1"/>
+    <col min="510" max="510" width="17.5703125" bestFit="1" customWidth="1"/>
+    <col min="511" max="511" width="35.140625" bestFit="1" customWidth="1"/>
+    <col min="512" max="512" width="61.140625" bestFit="1" customWidth="1"/>
+    <col min="513" max="513" width="47.140625" bestFit="1" customWidth="1"/>
+    <col min="514" max="514" width="58.42578125" bestFit="1" customWidth="1"/>
+    <col min="515" max="515" width="38.85546875" bestFit="1" customWidth="1"/>
+    <col min="516" max="516" width="28" bestFit="1" customWidth="1"/>
+    <col min="517" max="517" width="44.5703125" bestFit="1" customWidth="1"/>
+    <col min="518" max="518" width="29.28515625" bestFit="1" customWidth="1"/>
+    <col min="519" max="519" width="37" bestFit="1" customWidth="1"/>
+    <col min="520" max="520" width="34.7109375" bestFit="1" customWidth="1"/>
+    <col min="521" max="521" width="39.5703125" bestFit="1" customWidth="1"/>
+    <col min="522" max="522" width="82.28515625" bestFit="1" customWidth="1"/>
+    <col min="523" max="523" width="52.7109375" bestFit="1" customWidth="1"/>
+    <col min="524" max="524" width="54.5703125" bestFit="1" customWidth="1"/>
+    <col min="525" max="525" width="30.28515625" bestFit="1" customWidth="1"/>
+    <col min="526" max="526" width="52.7109375" bestFit="1" customWidth="1"/>
+    <col min="527" max="527" width="18.7109375" bestFit="1" customWidth="1"/>
+    <col min="528" max="528" width="37.140625" bestFit="1" customWidth="1"/>
+    <col min="529" max="529" width="70.42578125" bestFit="1" customWidth="1"/>
+    <col min="530" max="530" width="63.5703125" bestFit="1" customWidth="1"/>
+    <col min="531" max="531" width="48.5703125" bestFit="1" customWidth="1"/>
+    <col min="532" max="532" width="66.7109375" bestFit="1" customWidth="1"/>
+    <col min="533" max="533" width="34.5703125" bestFit="1" customWidth="1"/>
+    <col min="534" max="534" width="50.42578125" bestFit="1" customWidth="1"/>
+    <col min="535" max="535" width="35" bestFit="1" customWidth="1"/>
+    <col min="536" max="536" width="58.85546875" bestFit="1" customWidth="1"/>
+    <col min="537" max="537" width="41.85546875" bestFit="1" customWidth="1"/>
+    <col min="538" max="538" width="53.85546875" bestFit="1" customWidth="1"/>
+    <col min="539" max="539" width="48.28515625" bestFit="1" customWidth="1"/>
+    <col min="540" max="540" width="44.140625" bestFit="1" customWidth="1"/>
+    <col min="541" max="541" width="40.28515625" bestFit="1" customWidth="1"/>
+    <col min="542" max="542" width="34.7109375" bestFit="1" customWidth="1"/>
+    <col min="543" max="543" width="32.7109375" bestFit="1" customWidth="1"/>
+    <col min="544" max="544" width="46.5703125" bestFit="1" customWidth="1"/>
+    <col min="545" max="545" width="74.28515625" bestFit="1" customWidth="1"/>
+    <col min="546" max="546" width="29.5703125" bestFit="1" customWidth="1"/>
+    <col min="547" max="547" width="55.42578125" bestFit="1" customWidth="1"/>
+    <col min="548" max="548" width="64.7109375" bestFit="1" customWidth="1"/>
+    <col min="549" max="549" width="57.42578125" bestFit="1" customWidth="1"/>
+    <col min="550" max="550" width="60.5703125" bestFit="1" customWidth="1"/>
+    <col min="551" max="551" width="44" bestFit="1" customWidth="1"/>
+    <col min="552" max="552" width="20" bestFit="1" customWidth="1"/>
+    <col min="553" max="553" width="49.28515625" bestFit="1" customWidth="1"/>
+    <col min="554" max="554" width="37" bestFit="1" customWidth="1"/>
+    <col min="555" max="555" width="66.42578125" bestFit="1" customWidth="1"/>
+    <col min="556" max="556" width="61.5703125" bestFit="1" customWidth="1"/>
+    <col min="557" max="557" width="37.28515625" bestFit="1" customWidth="1"/>
+    <col min="558" max="558" width="61.140625" bestFit="1" customWidth="1"/>
+    <col min="559" max="559" width="58.7109375" bestFit="1" customWidth="1"/>
+    <col min="560" max="560" width="70.28515625" bestFit="1" customWidth="1"/>
+    <col min="561" max="561" width="30.7109375" bestFit="1" customWidth="1"/>
+    <col min="562" max="562" width="60.85546875" bestFit="1" customWidth="1"/>
+    <col min="563" max="563" width="23.7109375" bestFit="1" customWidth="1"/>
+    <col min="564" max="564" width="43.140625" bestFit="1" customWidth="1"/>
+    <col min="565" max="565" width="34.7109375" bestFit="1" customWidth="1"/>
+    <col min="566" max="566" width="37" bestFit="1" customWidth="1"/>
+    <col min="567" max="567" width="55.85546875" bestFit="1" customWidth="1"/>
+    <col min="568" max="568" width="23.42578125" bestFit="1" customWidth="1"/>
+    <col min="569" max="569" width="46" bestFit="1" customWidth="1"/>
+    <col min="570" max="570" width="51.7109375" bestFit="1" customWidth="1"/>
+    <col min="571" max="571" width="51" bestFit="1" customWidth="1"/>
+    <col min="572" max="572" width="28.5703125" bestFit="1" customWidth="1"/>
+    <col min="573" max="573" width="61" bestFit="1" customWidth="1"/>
+    <col min="574" max="574" width="38.28515625" bestFit="1" customWidth="1"/>
+    <col min="575" max="575" width="76.140625" bestFit="1" customWidth="1"/>
+    <col min="576" max="576" width="53" bestFit="1" customWidth="1"/>
+    <col min="577" max="577" width="25" bestFit="1" customWidth="1"/>
+    <col min="578" max="578" width="41.140625" bestFit="1" customWidth="1"/>
+    <col min="579" max="579" width="17.85546875" bestFit="1" customWidth="1"/>
+    <col min="580" max="580" width="35.140625" bestFit="1" customWidth="1"/>
+    <col min="581" max="581" width="40" bestFit="1" customWidth="1"/>
+    <col min="582" max="582" width="54.7109375" bestFit="1" customWidth="1"/>
+    <col min="583" max="583" width="39.28515625" bestFit="1" customWidth="1"/>
+    <col min="584" max="584" width="35.7109375" bestFit="1" customWidth="1"/>
+    <col min="585" max="585" width="57.28515625" bestFit="1" customWidth="1"/>
+    <col min="586" max="586" width="49.42578125" bestFit="1" customWidth="1"/>
+    <col min="587" max="587" width="52.140625" bestFit="1" customWidth="1"/>
+    <col min="588" max="588" width="30.28515625" bestFit="1" customWidth="1"/>
+    <col min="589" max="589" width="58.28515625" bestFit="1" customWidth="1"/>
+    <col min="590" max="590" width="54.7109375" bestFit="1" customWidth="1"/>
+    <col min="591" max="591" width="54" bestFit="1" customWidth="1"/>
+    <col min="592" max="592" width="67.7109375" bestFit="1" customWidth="1"/>
+    <col min="593" max="593" width="54.140625" bestFit="1" customWidth="1"/>
+    <col min="594" max="594" width="59.42578125" bestFit="1" customWidth="1"/>
+    <col min="595" max="595" width="51.28515625" bestFit="1" customWidth="1"/>
+    <col min="596" max="596" width="53.5703125" bestFit="1" customWidth="1"/>
+    <col min="597" max="597" width="69.7109375" bestFit="1" customWidth="1"/>
+    <col min="598" max="598" width="41.42578125" bestFit="1" customWidth="1"/>
+    <col min="599" max="599" width="20.7109375" bestFit="1" customWidth="1"/>
+    <col min="600" max="600" width="45.85546875" bestFit="1" customWidth="1"/>
+    <col min="601" max="601" width="30" bestFit="1" customWidth="1"/>
+    <col min="602" max="603" width="27.28515625" bestFit="1" customWidth="1"/>
+    <col min="604" max="604" width="37.7109375" bestFit="1" customWidth="1"/>
     <col min="605" max="605" width="18.85546875" bestFit="1" customWidth="1"/>
     <col min="606" max="606" width="43.85546875" bestFit="1" customWidth="1"/>
     <col min="607" max="607" width="38.28515625" bestFit="1" customWidth="1"/>
     <col min="608" max="608" width="33.85546875" bestFit="1" customWidth="1"/>
     <col min="609" max="609" width="45.5703125" bestFit="1" customWidth="1"/>
     <col min="610" max="610" width="21" bestFit="1" customWidth="1"/>
+    <col min="611" max="611" width="17.5703125" bestFit="1" customWidth="1"/>
+    <col min="612" max="612" width="103.85546875" bestFit="1" customWidth="1"/>
+    <col min="613" max="613" width="24.28515625" bestFit="1" customWidth="1"/>
+    <col min="614" max="614" width="33.42578125" bestFit="1" customWidth="1"/>
+    <col min="615" max="615" width="13.140625" bestFit="1" customWidth="1"/>
+    <col min="616" max="616" width="20.28515625" bestFit="1" customWidth="1"/>
+    <col min="617" max="617" width="23.28515625" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:618">

--- a/pantallas_android/orden_ludiyorden.xlsx
+++ b/pantallas_android/orden_ludiyorden.xlsx
@@ -1,11 +1,10 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="4" rupBuild="29127"/>
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+  <fileVersion appName="xl" lastEdited="5" lowestEdited="4" rupBuild="9303"/>
   <workbookPr filterPrivacy="1" defaultThemeVersion="124226"/>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{0F9223C5-F49D-4A5A-8E68-F72345ABFA48}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720"/>
   </bookViews>
   <sheets>
     <sheet name="FORMULARIO DE MTTO PREVENTIV 1" sheetId="1" r:id="rId1"/>
@@ -6104,7 +6103,7 @@
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <fonts count="2">
     <font>
       <sz val="11"/>
@@ -6186,9 +6185,9 @@
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
-<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office Theme 2007 - 2010">
+<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Tema de Office">
   <a:themeElements>
-    <a:clrScheme name="Office 2007 - 2010">
+    <a:clrScheme name="Office">
       <a:dk1>
         <a:sysClr val="windowText" lastClr="000000"/>
       </a:dk1>
@@ -6226,7 +6225,7 @@
         <a:srgbClr val="800080"/>
       </a:folHlink>
     </a:clrScheme>
-    <a:fontScheme name="Office 2007 - 2010">
+    <a:fontScheme name="Office">
       <a:majorFont>
         <a:latin typeface="Cambria"/>
         <a:ea typeface=""/>
@@ -6298,7 +6297,7 @@
         <a:font script="Geor" typeface="Sylfaen"/>
       </a:minorFont>
     </a:fontScheme>
-    <a:fmtScheme name="Office 2007 - 2010">
+    <a:fmtScheme name="Office">
       <a:fillStyleLst>
         <a:solidFill>
           <a:schemeClr val="phClr"/>
@@ -6471,14 +6470,14 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <dimension ref="A1:WT76"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="9.140625" defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="11.85546875" customWidth="1"/>
     <col min="2" max="2" width="18.85546875" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="24.28515625" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="10" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="12.140625" customWidth="1"/>
     <col min="5" max="5" width="17.42578125" bestFit="1" customWidth="1"/>
     <col min="6" max="6" width="49.7109375" bestFit="1" customWidth="1"/>
     <col min="7" max="8" width="18.42578125" bestFit="1" customWidth="1"/>
@@ -6774,7 +6773,7 @@
     <col min="300" max="300" width="40" bestFit="1" customWidth="1"/>
     <col min="301" max="301" width="40.42578125" bestFit="1" customWidth="1"/>
     <col min="302" max="302" width="37" bestFit="1" customWidth="1"/>
-    <col min="303" max="303" width="11.85546875" bestFit="1" customWidth="1"/>
+    <col min="303" max="303" width="17.5703125" customWidth="1"/>
     <col min="304" max="304" width="45" bestFit="1" customWidth="1"/>
     <col min="305" max="305" width="43.7109375" bestFit="1" customWidth="1"/>
     <col min="306" max="306" width="21" bestFit="1" customWidth="1"/>
@@ -21082,7 +21081,7 @@
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A2:WT2" xr:uid="{00000000-0001-0000-0000-000000000000}"/>
+  <autoFilter ref="A2:WT2"/>
   <mergeCells count="1">
     <mergeCell ref="WP1:WS1"/>
   </mergeCells>
@@ -21093,7 +21092,7 @@
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0100-000000000000}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <dimension ref="A1:WT150"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="9.140625" defaultRowHeight="15"/>
   <cols>
